--- a/events/LaSeu_2017_WC/LaSeu_2017_WC_start.xlsx
+++ b/events/LaSeu_2017_WC/LaSeu_2017_WC_start.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W639"/>
+  <dimension ref="A1:AC639"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,17 +519,47 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Name4</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Name5</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Name6</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
           <t>ICF_ID1</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>ICF_ID2</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>ICF_ID3</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>ICF_ID4</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>ICF_ID5</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>ICF_ID6</t>
         </is>
       </c>
     </row>
@@ -1353,12 +1383,12 @@
           <t>GEWISSLER Matus</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>39248</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="Y18" t="inlineStr">
         <is>
           <t>39249</t>
         </is>
@@ -1421,12 +1451,12 @@
           <t>HOCHSCHORNER Peter</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>35356</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="Y19" t="inlineStr">
         <is>
           <t>35357</t>
         </is>
@@ -1489,12 +1519,12 @@
           <t>CAMPORESI Pietro</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>35498</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="Y20" t="inlineStr">
         <is>
           <t>35497</t>
         </is>
@@ -1557,12 +1587,12 @@
           <t>VRZAN Jakub</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>35042</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="Y21" t="inlineStr">
         <is>
           <t>35043</t>
         </is>
@@ -1625,12 +1655,12 @@
           <t>PEREZ Jesus</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>35757</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
+      <c r="Y22" t="inlineStr">
         <is>
           <t>36091</t>
         </is>
@@ -1693,12 +1723,12 @@
           <t>BATIK Jan</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>35368</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
+      <c r="Y23" t="inlineStr">
         <is>
           <t>35367</t>
         </is>
@@ -1761,12 +1791,12 @@
           <t>BETTGE Nico</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>35145</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="Y24" t="inlineStr">
         <is>
           <t>35133</t>
         </is>
@@ -1829,12 +1859,12 @@
           <t>BISO Hugo</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>35403</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
+      <c r="Y25" t="inlineStr">
         <is>
           <t>35229</t>
         </is>
@@ -1897,12 +1927,12 @@
           <t>CAILHOL Hugo</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>35476</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
+      <c r="Y26" t="inlineStr">
         <is>
           <t>35491</t>
         </is>
@@ -1965,12 +1995,12 @@
           <t>JANE Jakub</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>35060</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr">
+      <c r="Y27" t="inlineStr">
         <is>
           <t>35061</t>
         </is>
@@ -2033,12 +2063,12 @@
           <t>BECKER Thomas</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>35139</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
+      <c r="Y28" t="inlineStr">
         <is>
           <t>35143</t>
         </is>
@@ -2101,12 +2131,12 @@
           <t>PECHE Matthieu</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>35350</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
+      <c r="Y29" t="inlineStr">
         <is>
           <t>35400</t>
         </is>
@@ -2169,12 +2199,12 @@
           <t>SINDLER Marek</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>35062</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr">
+      <c r="Y30" t="inlineStr">
         <is>
           <t>35063</t>
         </is>
@@ -2237,12 +2267,12 @@
           <t>SKANTAR Peter</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="X31" t="inlineStr">
         <is>
           <t>35360</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr">
+      <c r="Y31" t="inlineStr">
         <is>
           <t>35361</t>
         </is>
@@ -2300,7 +2330,7 @@
           <t>FORROW Bethan</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>69065</t>
         </is>
@@ -2358,7 +2388,7 @@
           <t>DIESKOVA Eva</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr">
+      <c r="X33" t="inlineStr">
         <is>
           <t>71639</t>
         </is>
@@ -2416,7 +2446,7 @@
           <t>ZHANG Jinjie</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr">
+      <c r="X34" t="inlineStr">
         <is>
           <t>72213</t>
         </is>
@@ -2474,7 +2504,7 @@
           <t>BAYLACQ Oceane</t>
         </is>
       </c>
-      <c r="U35" t="inlineStr">
+      <c r="X35" t="inlineStr">
         <is>
           <t>69444</t>
         </is>
@@ -2532,7 +2562,7 @@
           <t>YAZAWA Aki</t>
         </is>
       </c>
-      <c r="U36" t="inlineStr">
+      <c r="X36" t="inlineStr">
         <is>
           <t>36486</t>
         </is>
@@ -2590,7 +2620,7 @@
           <t>BREGAZZI Ella</t>
         </is>
       </c>
-      <c r="U37" t="inlineStr">
+      <c r="X37" t="inlineStr">
         <is>
           <t>41598</t>
         </is>
@@ -2701,7 +2731,7 @@
           <t>HAVLICKOVA Katerina</t>
         </is>
       </c>
-      <c r="U39" t="inlineStr">
+      <c r="X39" t="inlineStr">
         <is>
           <t>35048</t>
         </is>
@@ -2812,7 +2842,7 @@
           <t>DUANGLAWA Atcharaporn</t>
         </is>
       </c>
-      <c r="U41" t="inlineStr">
+      <c r="X41" t="inlineStr">
         <is>
           <t>61799</t>
         </is>
@@ -2870,7 +2900,7 @@
           <t>ESTACIA NETA Omira</t>
         </is>
       </c>
-      <c r="U42" t="inlineStr">
+      <c r="X42" t="inlineStr">
         <is>
           <t>60494</t>
         </is>
@@ -2928,7 +2958,7 @@
           <t>O'FERRALL Caoimhe</t>
         </is>
       </c>
-      <c r="U43" t="inlineStr">
+      <c r="X43" t="inlineStr">
         <is>
           <t>61007</t>
         </is>
@@ -2986,7 +3016,7 @@
           <t>YAGI Airi</t>
         </is>
       </c>
-      <c r="U44" t="inlineStr">
+      <c r="X44" t="inlineStr">
         <is>
           <t>37756</t>
         </is>
@@ -3097,7 +3127,7 @@
           <t>CHEN Shi</t>
         </is>
       </c>
-      <c r="U46" t="inlineStr">
+      <c r="X46" t="inlineStr">
         <is>
           <t>52027</t>
         </is>
@@ -3155,7 +3185,7 @@
           <t>TRAVERS Kelly</t>
         </is>
       </c>
-      <c r="U47" t="inlineStr">
+      <c r="X47" t="inlineStr">
         <is>
           <t>51643</t>
         </is>
@@ -3213,7 +3243,7 @@
           <t>PELLICER CHICA Laura</t>
         </is>
       </c>
-      <c r="U48" t="inlineStr">
+      <c r="X48" t="inlineStr">
         <is>
           <t>43129</t>
         </is>
@@ -3271,7 +3301,7 @@
           <t>DANIELS Haley</t>
         </is>
       </c>
-      <c r="U49" t="inlineStr">
+      <c r="X49" t="inlineStr">
         <is>
           <t>36260</t>
         </is>
@@ -3382,7 +3412,7 @@
           <t>KOZOROG Alja</t>
         </is>
       </c>
-      <c r="U51" t="inlineStr">
+      <c r="X51" t="inlineStr">
         <is>
           <t>39986</t>
         </is>
@@ -3440,7 +3470,7 @@
           <t>JONES Luuka</t>
         </is>
       </c>
-      <c r="U52" t="inlineStr">
+      <c r="X52" t="inlineStr">
         <is>
           <t>36657</t>
         </is>
@@ -3498,7 +3528,7 @@
           <t>BIZJAK Nina</t>
         </is>
       </c>
-      <c r="U53" t="inlineStr">
+      <c r="X53" t="inlineStr">
         <is>
           <t>39984</t>
         </is>
@@ -3609,7 +3639,7 @@
           <t>OHMAYER Birgit</t>
         </is>
       </c>
-      <c r="U55" t="inlineStr">
+      <c r="X55" t="inlineStr">
         <is>
           <t>39157</t>
         </is>
@@ -3667,7 +3697,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U56" t="inlineStr">
+      <c r="X56" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -3725,7 +3755,7 @@
           <t>STANOVSKA Sona</t>
         </is>
       </c>
-      <c r="U57" t="inlineStr">
+      <c r="X57" t="inlineStr">
         <is>
           <t>51647</t>
         </is>
@@ -3783,7 +3813,7 @@
           <t>HERZOG Andrea</t>
         </is>
       </c>
-      <c r="U58" t="inlineStr">
+      <c r="X58" t="inlineStr">
         <is>
           <t>55099</t>
         </is>
@@ -3841,7 +3871,7 @@
           <t>MACEKOVA Simona</t>
         </is>
       </c>
-      <c r="U59" t="inlineStr">
+      <c r="X59" t="inlineStr">
         <is>
           <t>45153</t>
         </is>
@@ -3899,7 +3929,7 @@
           <t>SABITOVA Zulfia</t>
         </is>
       </c>
-      <c r="U60" t="inlineStr">
+      <c r="X60" t="inlineStr">
         <is>
           <t>40572</t>
         </is>
@@ -3957,7 +3987,7 @@
           <t>OLAZABAL Klara</t>
         </is>
       </c>
-      <c r="U61" t="inlineStr">
+      <c r="X61" t="inlineStr">
         <is>
           <t>43985</t>
         </is>
@@ -4015,7 +4045,7 @@
           <t>TIXIER Cecile</t>
         </is>
       </c>
-      <c r="U62" t="inlineStr">
+      <c r="X62" t="inlineStr">
         <is>
           <t>35687</t>
         </is>
@@ -4073,7 +4103,7 @@
           <t>JANCOVA Monika</t>
         </is>
       </c>
-      <c r="U63" t="inlineStr">
+      <c r="X63" t="inlineStr">
         <is>
           <t>36015</t>
         </is>
@@ -4131,7 +4161,7 @@
           <t>STOECKLIN Lena</t>
         </is>
       </c>
-      <c r="U64" t="inlineStr">
+      <c r="X64" t="inlineStr">
         <is>
           <t>35822</t>
         </is>
@@ -4189,7 +4219,7 @@
           <t>MUKHGALEEVA Polina</t>
         </is>
       </c>
-      <c r="U65" t="inlineStr">
+      <c r="X65" t="inlineStr">
         <is>
           <t>35768</t>
         </is>
@@ -4247,7 +4277,7 @@
           <t>PRIOUX Lucie</t>
         </is>
       </c>
-      <c r="U66" t="inlineStr">
+      <c r="X66" t="inlineStr">
         <is>
           <t>42984</t>
         </is>
@@ -4305,7 +4335,7 @@
           <t>FOX Noemie</t>
         </is>
       </c>
-      <c r="U67" t="inlineStr">
+      <c r="X67" t="inlineStr">
         <is>
           <t>44812</t>
         </is>
@@ -4363,7 +4393,7 @@
           <t>VAN DER KNIJFF Annebel</t>
         </is>
       </c>
-      <c r="U68" t="inlineStr">
+      <c r="X68" t="inlineStr">
         <is>
           <t>39945</t>
         </is>
@@ -4421,7 +4451,7 @@
           <t>GIBSON Eilidh</t>
         </is>
       </c>
-      <c r="U69" t="inlineStr">
+      <c r="X69" t="inlineStr">
         <is>
           <t>36708</t>
         </is>
@@ -4479,7 +4509,7 @@
           <t>SATILA Ana</t>
         </is>
       </c>
-      <c r="U70" t="inlineStr">
+      <c r="X70" t="inlineStr">
         <is>
           <t>35327</t>
         </is>
@@ -4537,7 +4567,7 @@
           <t>WERATSCHNIG Nadine</t>
         </is>
       </c>
-      <c r="U71" t="inlineStr">
+      <c r="X71" t="inlineStr">
         <is>
           <t>41613</t>
         </is>
@@ -4595,7 +4625,7 @@
           <t>LAWRENCE Rosalyn</t>
         </is>
       </c>
-      <c r="U72" t="inlineStr">
+      <c r="X72" t="inlineStr">
         <is>
           <t>36531</t>
         </is>
@@ -4706,7 +4736,7 @@
           <t>JACQUET Claire</t>
         </is>
       </c>
-      <c r="U74" t="inlineStr">
+      <c r="X74" t="inlineStr">
         <is>
           <t>35684</t>
         </is>
@@ -4764,7 +4794,7 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U75" t="inlineStr">
+      <c r="X75" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -4822,7 +4852,7 @@
           <t>FRANKLIN Mallory</t>
         </is>
       </c>
-      <c r="U76" t="inlineStr">
+      <c r="X76" t="inlineStr">
         <is>
           <t>35615</t>
         </is>
@@ -4880,7 +4910,7 @@
           <t>VILARRUBLA Nuria</t>
         </is>
       </c>
-      <c r="U77" t="inlineStr">
+      <c r="X77" t="inlineStr">
         <is>
           <t>35746</t>
         </is>
@@ -4938,7 +4968,7 @@
           <t>WOODS Kimberley</t>
         </is>
       </c>
-      <c r="U78" t="inlineStr">
+      <c r="X78" t="inlineStr">
         <is>
           <t>35650</t>
         </is>
@@ -4996,7 +5026,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U79" t="inlineStr">
+      <c r="X79" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -5054,7 +5084,7 @@
           <t>ATKINS Austin</t>
         </is>
       </c>
-      <c r="U80" t="inlineStr">
+      <c r="X80" t="inlineStr">
         <is>
           <t>80421</t>
         </is>
@@ -5112,7 +5142,7 @@
           <t>PITTMAN Taylor</t>
         </is>
       </c>
-      <c r="U81" t="inlineStr">
+      <c r="X81" t="inlineStr">
         <is>
           <t>69137</t>
         </is>
@@ -5170,7 +5200,7 @@
           <t>JOSEPH Joshua</t>
         </is>
       </c>
-      <c r="U82" t="inlineStr">
+      <c r="X82" t="inlineStr">
         <is>
           <t>69141</t>
         </is>
@@ -5228,7 +5258,7 @@
           <t>HUANG Cunguang</t>
         </is>
       </c>
-      <c r="U83" t="inlineStr">
+      <c r="X83" t="inlineStr">
         <is>
           <t>75492</t>
         </is>
@@ -5286,7 +5316,7 @@
           <t>RYAN Cade</t>
         </is>
       </c>
-      <c r="U84" t="inlineStr">
+      <c r="X84" t="inlineStr">
         <is>
           <t>37919</t>
         </is>
@@ -5344,7 +5374,7 @@
           <t>ALVARENGA Frederico</t>
         </is>
       </c>
-      <c r="U85" t="inlineStr">
+      <c r="X85" t="inlineStr">
         <is>
           <t>71976</t>
         </is>
@@ -5402,7 +5432,7 @@
           <t>VIANELLO Marco</t>
         </is>
       </c>
-      <c r="U86" t="inlineStr">
+      <c r="X86" t="inlineStr">
         <is>
           <t>54910</t>
         </is>
@@ -5460,7 +5490,7 @@
           <t>KORPES Ren</t>
         </is>
       </c>
-      <c r="U87" t="inlineStr">
+      <c r="X87" t="inlineStr">
         <is>
           <t>39941</t>
         </is>
@@ -5518,7 +5548,7 @@
           <t>KUDER MARUSIC Vid</t>
         </is>
       </c>
-      <c r="U88" t="inlineStr">
+      <c r="X88" t="inlineStr">
         <is>
           <t>44342</t>
         </is>
@@ -5576,7 +5606,7 @@
           <t>PRIGENT Yves</t>
         </is>
       </c>
-      <c r="U89" t="inlineStr">
+      <c r="X89" t="inlineStr">
         <is>
           <t>35671</t>
         </is>
@@ -5634,7 +5664,7 @@
           <t>NGAMSANGA Paitas</t>
         </is>
       </c>
-      <c r="U90" t="inlineStr">
+      <c r="X90" t="inlineStr">
         <is>
           <t>68857</t>
         </is>
@@ -5692,7 +5722,7 @@
           <t>ECHEVERRIA OLGUIN Andraz</t>
         </is>
       </c>
-      <c r="U91" t="inlineStr">
+      <c r="X91" t="inlineStr">
         <is>
           <t>41646</t>
         </is>
@@ -5750,7 +5780,7 @@
           <t>TEAGUE Eoin</t>
         </is>
       </c>
-      <c r="U92" t="inlineStr">
+      <c r="X92" t="inlineStr">
         <is>
           <t>37913</t>
         </is>
@@ -5808,7 +5838,7 @@
           <t>HELLARD Suworna</t>
         </is>
       </c>
-      <c r="U93" t="inlineStr">
+      <c r="X93" t="inlineStr">
         <is>
           <t>43088</t>
         </is>
@@ -5866,7 +5896,7 @@
           <t>MARTIN Gerome</t>
         </is>
       </c>
-      <c r="U94" t="inlineStr">
+      <c r="X94" t="inlineStr">
         <is>
           <t>36720</t>
         </is>
@@ -5924,7 +5954,7 @@
           <t>CURTIS Samuel</t>
         </is>
       </c>
-      <c r="U95" t="inlineStr">
+      <c r="X95" t="inlineStr">
         <is>
           <t>36683</t>
         </is>
@@ -5982,7 +6012,7 @@
           <t>SOARES Renan</t>
         </is>
       </c>
-      <c r="U96" t="inlineStr">
+      <c r="X96" t="inlineStr">
         <is>
           <t>42776</t>
         </is>
@@ -6040,7 +6070,7 @@
           <t>MIKO Radoslav</t>
         </is>
       </c>
-      <c r="U97" t="inlineStr">
+      <c r="X97" t="inlineStr">
         <is>
           <t>71930</t>
         </is>
@@ -6098,7 +6128,7 @@
           <t>KANAYA Tohru</t>
         </is>
       </c>
-      <c r="U98" t="inlineStr">
+      <c r="X98" t="inlineStr">
         <is>
           <t>36484</t>
         </is>
@@ -6156,7 +6186,7 @@
           <t>YOSHIDA Taku</t>
         </is>
       </c>
-      <c r="U99" t="inlineStr">
+      <c r="X99" t="inlineStr">
         <is>
           <t>41611</t>
         </is>
@@ -6214,7 +6244,7 @@
           <t>MAPELLI Guilherme Marcello</t>
         </is>
       </c>
-      <c r="U100" t="inlineStr">
+      <c r="X100" t="inlineStr">
         <is>
           <t>38015</t>
         </is>
@@ -6272,7 +6302,7 @@
           <t>CHIARELLO Gelindo</t>
         </is>
       </c>
-      <c r="U101" t="inlineStr">
+      <c r="X101" t="inlineStr">
         <is>
           <t>39956</t>
         </is>
@@ -6330,7 +6360,7 @@
           <t>STANOVSKY Martin</t>
         </is>
       </c>
-      <c r="U102" t="inlineStr">
+      <c r="X102" t="inlineStr">
         <is>
           <t>68782</t>
         </is>
@@ -6388,7 +6418,7 @@
           <t>FORD David</t>
         </is>
       </c>
-      <c r="U103" t="inlineStr">
+      <c r="X103" t="inlineStr">
         <is>
           <t>35532</t>
         </is>
@@ -6446,7 +6476,7 @@
           <t>WAHLEN Fredrik</t>
         </is>
       </c>
-      <c r="U104" t="inlineStr">
+      <c r="X104" t="inlineStr">
         <is>
           <t>35102</t>
         </is>
@@ -6504,7 +6534,7 @@
           <t>QUAN Xin</t>
         </is>
       </c>
-      <c r="U105" t="inlineStr">
+      <c r="X105" t="inlineStr">
         <is>
           <t>62343</t>
         </is>
@@ -6562,7 +6592,7 @@
           <t>BOWERS Christopher</t>
         </is>
       </c>
-      <c r="U106" t="inlineStr">
+      <c r="X106" t="inlineStr">
         <is>
           <t>52010</t>
         </is>
@@ -6620,7 +6650,7 @@
           <t>TAYLER Michael</t>
         </is>
       </c>
-      <c r="U107" t="inlineStr">
+      <c r="X107" t="inlineStr">
         <is>
           <t>36262</t>
         </is>
@@ -6678,7 +6708,7 @@
           <t>MACUS Richard</t>
         </is>
       </c>
-      <c r="U108" t="inlineStr">
+      <c r="X108" t="inlineStr">
         <is>
           <t>42855</t>
         </is>
@@ -6736,7 +6766,7 @@
           <t>TRAVOSTINO Benjamin</t>
         </is>
       </c>
-      <c r="U109" t="inlineStr">
+      <c r="X109" t="inlineStr">
         <is>
           <t>68795</t>
         </is>
@@ -6794,7 +6824,7 @@
           <t>SILVA Ivan</t>
         </is>
       </c>
-      <c r="U110" t="inlineStr">
+      <c r="X110" t="inlineStr">
         <is>
           <t>35482</t>
         </is>
@@ -6852,7 +6882,7 @@
           <t>JAKSE Zan</t>
         </is>
       </c>
-      <c r="U111" t="inlineStr">
+      <c r="X111" t="inlineStr">
         <is>
           <t>44340</t>
         </is>
@@ -6910,7 +6940,7 @@
           <t>DRAPER Warwick</t>
         </is>
       </c>
-      <c r="U112" t="inlineStr">
+      <c r="X112" t="inlineStr">
         <is>
           <t>36536</t>
         </is>
@@ -6968,7 +6998,7 @@
           <t>YAZAWA Kazuki</t>
         </is>
       </c>
-      <c r="U113" t="inlineStr">
+      <c r="X113" t="inlineStr">
         <is>
           <t>36482</t>
         </is>
@@ -7026,7 +7056,7 @@
           <t>WEGER Jakob</t>
         </is>
       </c>
-      <c r="U114" t="inlineStr">
+      <c r="X114" t="inlineStr">
         <is>
           <t>54909</t>
         </is>
@@ -7084,7 +7114,7 @@
           <t>PASIUT Michal</t>
         </is>
       </c>
-      <c r="U115" t="inlineStr">
+      <c r="X115" t="inlineStr">
         <is>
           <t>35095</t>
         </is>
@@ -7142,7 +7172,7 @@
           <t>WEGER Matthias</t>
         </is>
       </c>
-      <c r="U116" t="inlineStr">
+      <c r="X116" t="inlineStr">
         <is>
           <t>68837</t>
         </is>
@@ -7200,7 +7230,7 @@
           <t>TSVIET Igor</t>
         </is>
       </c>
-      <c r="U117" t="inlineStr">
+      <c r="X117" t="inlineStr">
         <is>
           <t>35527</t>
         </is>
@@ -7258,7 +7288,7 @@
           <t>HOLMER Erik</t>
         </is>
       </c>
-      <c r="U118" t="inlineStr">
+      <c r="X118" t="inlineStr">
         <is>
           <t>35104</t>
         </is>
@@ -7316,7 +7346,7 @@
           <t>BUTCHER Finn</t>
         </is>
       </c>
-      <c r="U119" t="inlineStr">
+      <c r="X119" t="inlineStr">
         <is>
           <t>36663</t>
         </is>
@@ -7374,7 +7404,7 @@
           <t>POTOCNY Marcel</t>
         </is>
       </c>
-      <c r="U120" t="inlineStr">
+      <c r="X120" t="inlineStr">
         <is>
           <t>35235</t>
         </is>
@@ -7432,7 +7462,7 @@
           <t>LLORENTE David</t>
         </is>
       </c>
-      <c r="U121" t="inlineStr">
+      <c r="X121" t="inlineStr">
         <is>
           <t>51850</t>
         </is>
@@ -7490,7 +7520,7 @@
           <t>GILBERT Callum</t>
         </is>
       </c>
-      <c r="U122" t="inlineStr">
+      <c r="X122" t="inlineStr">
         <is>
           <t>42090</t>
         </is>
@@ -7601,7 +7631,7 @@
           <t>LEITNER Mario</t>
         </is>
       </c>
-      <c r="U124" t="inlineStr">
+      <c r="X124" t="inlineStr">
         <is>
           <t>35546</t>
         </is>
@@ -7659,7 +7689,7 @@
           <t>OSCHMAUTZ Felix</t>
         </is>
       </c>
-      <c r="U125" t="inlineStr">
+      <c r="X125" t="inlineStr">
         <is>
           <t>51856</t>
         </is>
@@ -7717,7 +7747,7 @@
           <t>SRABOTNIK Martin</t>
         </is>
       </c>
-      <c r="U126" t="inlineStr">
+      <c r="X126" t="inlineStr">
         <is>
           <t>39080</t>
         </is>
@@ -7775,7 +7805,7 @@
           <t>DAWSON Mike</t>
         </is>
       </c>
-      <c r="U127" t="inlineStr">
+      <c r="X127" t="inlineStr">
         <is>
           <t>36656</t>
         </is>
@@ -7833,7 +7863,7 @@
           <t>IVALDI Zeno</t>
         </is>
       </c>
-      <c r="U128" t="inlineStr">
+      <c r="X128" t="inlineStr">
         <is>
           <t>35480</t>
         </is>
@@ -7891,7 +7921,7 @@
           <t>OHRSTROM Isak</t>
         </is>
       </c>
-      <c r="U129" t="inlineStr">
+      <c r="X129" t="inlineStr">
         <is>
           <t>35101</t>
         </is>
@@ -7949,7 +7979,7 @@
           <t>LAUNAY Antoine</t>
         </is>
       </c>
-      <c r="U130" t="inlineStr">
+      <c r="X130" t="inlineStr">
         <is>
           <t>68776</t>
         </is>
@@ -8007,7 +8037,7 @@
           <t>EIGEL Pavel</t>
         </is>
       </c>
-      <c r="U131" t="inlineStr">
+      <c r="X131" t="inlineStr">
         <is>
           <t>35458</t>
         </is>
@@ -8065,7 +8095,7 @@
           <t>CRESPO Joan</t>
         </is>
       </c>
-      <c r="U132" t="inlineStr">
+      <c r="X132" t="inlineStr">
         <is>
           <t>35749</t>
         </is>
@@ -8123,7 +8153,7 @@
           <t>DOBY Mathieu</t>
         </is>
       </c>
-      <c r="U133" t="inlineStr">
+      <c r="X133" t="inlineStr">
         <is>
           <t>35292</t>
         </is>
@@ -8181,7 +8211,7 @@
           <t>SCHWEIKERT Fabian</t>
         </is>
       </c>
-      <c r="U134" t="inlineStr">
+      <c r="X134" t="inlineStr">
         <is>
           <t>38412</t>
         </is>
@@ -8239,7 +8269,7 @@
           <t>HRADILEK Vavrinec</t>
         </is>
       </c>
-      <c r="U135" t="inlineStr">
+      <c r="X135" t="inlineStr">
         <is>
           <t>35031</t>
         </is>
@@ -8297,7 +8327,7 @@
           <t>NEVEU Boris</t>
         </is>
       </c>
-      <c r="U136" t="inlineStr">
+      <c r="X136" t="inlineStr">
         <is>
           <t>35396</t>
         </is>
@@ -8355,7 +8385,7 @@
           <t>FORBES-CRYANS Bradley</t>
         </is>
       </c>
-      <c r="U137" t="inlineStr">
+      <c r="X137" t="inlineStr">
         <is>
           <t>36513</t>
         </is>
@@ -8413,7 +8443,7 @@
           <t>CLARKE Joseph</t>
         </is>
       </c>
-      <c r="U138" t="inlineStr">
+      <c r="X138" t="inlineStr">
         <is>
           <t>35654</t>
         </is>
@@ -8471,7 +8501,7 @@
           <t>POPIELA Dariusz</t>
         </is>
       </c>
-      <c r="U139" t="inlineStr">
+      <c r="X139" t="inlineStr">
         <is>
           <t>35096</t>
         </is>
@@ -8529,7 +8559,7 @@
           <t>SMOLEN Michal</t>
         </is>
       </c>
-      <c r="U140" t="inlineStr">
+      <c r="X140" t="inlineStr">
         <is>
           <t>36397</t>
         </is>
@@ -8587,7 +8617,7 @@
           <t>POLACZYK Mateusz</t>
         </is>
       </c>
-      <c r="U141" t="inlineStr">
+      <c r="X141" t="inlineStr">
         <is>
           <t>35072</t>
         </is>
@@ -8645,7 +8675,7 @@
           <t>COMBOT Sebastien</t>
         </is>
       </c>
-      <c r="U142" t="inlineStr">
+      <c r="X142" t="inlineStr">
         <is>
           <t>35234</t>
         </is>
@@ -8703,7 +8733,7 @@
           <t>GRIMM Alexander</t>
         </is>
       </c>
-      <c r="U143" t="inlineStr">
+      <c r="X143" t="inlineStr">
         <is>
           <t>35112</t>
         </is>
@@ -8761,7 +8791,7 @@
           <t>BIAZIZZO Mathieu</t>
         </is>
       </c>
-      <c r="U144" t="inlineStr">
+      <c r="X144" t="inlineStr">
         <is>
           <t>35484</t>
         </is>
@@ -8819,7 +8849,7 @@
           <t>TUNKA Ondrej</t>
         </is>
       </c>
-      <c r="U145" t="inlineStr">
+      <c r="X145" t="inlineStr">
         <is>
           <t>35947</t>
         </is>
@@ -8877,7 +8907,7 @@
           <t>HERNANZ Samuel</t>
         </is>
       </c>
-      <c r="U146" t="inlineStr">
+      <c r="X146" t="inlineStr">
         <is>
           <t>35786</t>
         </is>
@@ -8935,7 +8965,7 @@
           <t>DELFOUR Lucien</t>
         </is>
       </c>
-      <c r="U147" t="inlineStr">
+      <c r="X147" t="inlineStr">
         <is>
           <t>36537</t>
         </is>
@@ -8993,7 +9023,7 @@
           <t>BERSINGER Thomas</t>
         </is>
       </c>
-      <c r="U148" t="inlineStr">
+      <c r="X148" t="inlineStr">
         <is>
           <t>35228</t>
         </is>
@@ -9051,7 +9081,7 @@
           <t>DE GENNARO Giovanni</t>
         </is>
       </c>
-      <c r="U149" t="inlineStr">
+      <c r="X149" t="inlineStr">
         <is>
           <t>35244</t>
         </is>
@@ -9109,7 +9139,7 @@
           <t>SCHUBERT Sebastian</t>
         </is>
       </c>
-      <c r="U150" t="inlineStr">
+      <c r="X150" t="inlineStr">
         <is>
           <t>35114</t>
         </is>
@@ -9167,7 +9197,7 @@
           <t>GRIGAR Jakub</t>
         </is>
       </c>
-      <c r="U151" t="inlineStr">
+      <c r="X151" t="inlineStr">
         <is>
           <t>37284</t>
         </is>
@@ -9225,7 +9255,7 @@
           <t>AIGNER Hannes</t>
         </is>
       </c>
-      <c r="U152" t="inlineStr">
+      <c r="X152" t="inlineStr">
         <is>
           <t>35115</t>
         </is>
@@ -9283,7 +9313,7 @@
           <t>KAUZER Peter</t>
         </is>
       </c>
-      <c r="U153" t="inlineStr">
+      <c r="X153" t="inlineStr">
         <is>
           <t>35589</t>
         </is>
@@ -9341,7 +9371,7 @@
           <t>PRINDIS Vit</t>
         </is>
       </c>
-      <c r="U154" t="inlineStr">
+      <c r="X154" t="inlineStr">
         <is>
           <t>35065</t>
         </is>
@@ -9399,7 +9429,7 @@
           <t>PRSKAVEC Jiri</t>
         </is>
       </c>
-      <c r="U155" t="inlineStr">
+      <c r="X155" t="inlineStr">
         <is>
           <t>35033</t>
         </is>
@@ -9457,7 +9487,7 @@
           <t>FORROW Bethan</t>
         </is>
       </c>
-      <c r="U156" t="inlineStr">
+      <c r="X156" t="inlineStr">
         <is>
           <t>69065</t>
         </is>
@@ -9515,7 +9545,7 @@
           <t>DIESKOVA Eva</t>
         </is>
       </c>
-      <c r="U157" t="inlineStr">
+      <c r="X157" t="inlineStr">
         <is>
           <t>71639</t>
         </is>
@@ -9573,7 +9603,7 @@
           <t>ZHANG Jinjie</t>
         </is>
       </c>
-      <c r="U158" t="inlineStr">
+      <c r="X158" t="inlineStr">
         <is>
           <t>72213</t>
         </is>
@@ -9631,7 +9661,7 @@
           <t>BAYLACQ Oceane</t>
         </is>
       </c>
-      <c r="U159" t="inlineStr">
+      <c r="X159" t="inlineStr">
         <is>
           <t>69444</t>
         </is>
@@ -9689,7 +9719,7 @@
           <t>YAZAWA Aki</t>
         </is>
       </c>
-      <c r="U160" t="inlineStr">
+      <c r="X160" t="inlineStr">
         <is>
           <t>36486</t>
         </is>
@@ -9800,7 +9830,7 @@
           <t>HAVLICKOVA Katerina</t>
         </is>
       </c>
-      <c r="U162" t="inlineStr">
+      <c r="X162" t="inlineStr">
         <is>
           <t>35048</t>
         </is>
@@ -9911,7 +9941,7 @@
           <t>DUANGLAWA Atcharaporn</t>
         </is>
       </c>
-      <c r="U164" t="inlineStr">
+      <c r="X164" t="inlineStr">
         <is>
           <t>61799</t>
         </is>
@@ -9969,7 +9999,7 @@
           <t>ESTACIA NETA Omira</t>
         </is>
       </c>
-      <c r="U165" t="inlineStr">
+      <c r="X165" t="inlineStr">
         <is>
           <t>60494</t>
         </is>
@@ -10027,7 +10057,7 @@
           <t>O'FERRALL Caoimhe</t>
         </is>
       </c>
-      <c r="U166" t="inlineStr">
+      <c r="X166" t="inlineStr">
         <is>
           <t>61007</t>
         </is>
@@ -10085,7 +10115,7 @@
           <t>YAGI Airi</t>
         </is>
       </c>
-      <c r="U167" t="inlineStr">
+      <c r="X167" t="inlineStr">
         <is>
           <t>37756</t>
         </is>
@@ -10196,7 +10226,7 @@
           <t>CHEN Shi</t>
         </is>
       </c>
-      <c r="U169" t="inlineStr">
+      <c r="X169" t="inlineStr">
         <is>
           <t>52027</t>
         </is>
@@ -10254,7 +10284,7 @@
           <t>TRAVERS Kelly</t>
         </is>
       </c>
-      <c r="U170" t="inlineStr">
+      <c r="X170" t="inlineStr">
         <is>
           <t>51643</t>
         </is>
@@ -10312,7 +10342,7 @@
           <t>PELLICER CHICA Laura</t>
         </is>
       </c>
-      <c r="U171" t="inlineStr">
+      <c r="X171" t="inlineStr">
         <is>
           <t>43129</t>
         </is>
@@ -10370,7 +10400,7 @@
           <t>DANIELS Haley</t>
         </is>
       </c>
-      <c r="U172" t="inlineStr">
+      <c r="X172" t="inlineStr">
         <is>
           <t>36260</t>
         </is>
@@ -10481,7 +10511,7 @@
           <t>KOZOROG Alja</t>
         </is>
       </c>
-      <c r="U174" t="inlineStr">
+      <c r="X174" t="inlineStr">
         <is>
           <t>39986</t>
         </is>
@@ -10539,7 +10569,7 @@
           <t>JONES Luuka</t>
         </is>
       </c>
-      <c r="U175" t="inlineStr">
+      <c r="X175" t="inlineStr">
         <is>
           <t>36657</t>
         </is>
@@ -10597,7 +10627,7 @@
           <t>BIZJAK Nina</t>
         </is>
       </c>
-      <c r="U176" t="inlineStr">
+      <c r="X176" t="inlineStr">
         <is>
           <t>39984</t>
         </is>
@@ -10655,7 +10685,7 @@
           <t>OHMAYER Birgit</t>
         </is>
       </c>
-      <c r="U177" t="inlineStr">
+      <c r="X177" t="inlineStr">
         <is>
           <t>39157</t>
         </is>
@@ -10713,7 +10743,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U178" t="inlineStr">
+      <c r="X178" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -10771,7 +10801,7 @@
           <t>STANOVSKA Sona</t>
         </is>
       </c>
-      <c r="U179" t="inlineStr">
+      <c r="X179" t="inlineStr">
         <is>
           <t>51647</t>
         </is>
@@ -10829,7 +10859,7 @@
           <t>MACEKOVA Simona</t>
         </is>
       </c>
-      <c r="U180" t="inlineStr">
+      <c r="X180" t="inlineStr">
         <is>
           <t>45153</t>
         </is>
@@ -10887,7 +10917,7 @@
           <t>SATILA Ana</t>
         </is>
       </c>
-      <c r="U181" t="inlineStr">
+      <c r="X181" t="inlineStr">
         <is>
           <t>35327</t>
         </is>
@@ -10945,7 +10975,7 @@
           <t>WERATSCHNIG Nadine</t>
         </is>
       </c>
-      <c r="U182" t="inlineStr">
+      <c r="X182" t="inlineStr">
         <is>
           <t>41613</t>
         </is>
@@ -11003,7 +11033,7 @@
           <t>WOODS Kimberley</t>
         </is>
       </c>
-      <c r="U183" t="inlineStr">
+      <c r="X183" t="inlineStr">
         <is>
           <t>35650</t>
         </is>
@@ -11061,7 +11091,7 @@
           <t>ATKINS Austin</t>
         </is>
       </c>
-      <c r="U184" t="inlineStr">
+      <c r="X184" t="inlineStr">
         <is>
           <t>80421</t>
         </is>
@@ -11119,7 +11149,7 @@
           <t>PITTMAN Taylor</t>
         </is>
       </c>
-      <c r="U185" t="inlineStr">
+      <c r="X185" t="inlineStr">
         <is>
           <t>69137</t>
         </is>
@@ -11177,7 +11207,7 @@
           <t>JOSEPH Joshua</t>
         </is>
       </c>
-      <c r="U186" t="inlineStr">
+      <c r="X186" t="inlineStr">
         <is>
           <t>69141</t>
         </is>
@@ -11235,7 +11265,7 @@
           <t>HUANG Cunguang</t>
         </is>
       </c>
-      <c r="U187" t="inlineStr">
+      <c r="X187" t="inlineStr">
         <is>
           <t>75492</t>
         </is>
@@ -11293,7 +11323,7 @@
           <t>RYAN Cade</t>
         </is>
       </c>
-      <c r="U188" t="inlineStr">
+      <c r="X188" t="inlineStr">
         <is>
           <t>37919</t>
         </is>
@@ -11351,7 +11381,7 @@
           <t>ALVARENGA Frederico</t>
         </is>
       </c>
-      <c r="U189" t="inlineStr">
+      <c r="X189" t="inlineStr">
         <is>
           <t>71976</t>
         </is>
@@ -11409,7 +11439,7 @@
           <t>KORPES Ren</t>
         </is>
       </c>
-      <c r="U190" t="inlineStr">
+      <c r="X190" t="inlineStr">
         <is>
           <t>39941</t>
         </is>
@@ -11467,7 +11497,7 @@
           <t>KUDER MARUSIC Vid</t>
         </is>
       </c>
-      <c r="U191" t="inlineStr">
+      <c r="X191" t="inlineStr">
         <is>
           <t>44342</t>
         </is>
@@ -11525,7 +11555,7 @@
           <t>NGAMSANGA Paitas</t>
         </is>
       </c>
-      <c r="U192" t="inlineStr">
+      <c r="X192" t="inlineStr">
         <is>
           <t>68857</t>
         </is>
@@ -11583,7 +11613,7 @@
           <t>ECHEVERRIA OLGUIN Andraz</t>
         </is>
       </c>
-      <c r="U193" t="inlineStr">
+      <c r="X193" t="inlineStr">
         <is>
           <t>41646</t>
         </is>
@@ -11641,7 +11671,7 @@
           <t>TEAGUE Eoin</t>
         </is>
       </c>
-      <c r="U194" t="inlineStr">
+      <c r="X194" t="inlineStr">
         <is>
           <t>37913</t>
         </is>
@@ -11699,7 +11729,7 @@
           <t>HELLARD Suworna</t>
         </is>
       </c>
-      <c r="U195" t="inlineStr">
+      <c r="X195" t="inlineStr">
         <is>
           <t>43088</t>
         </is>
@@ -11757,7 +11787,7 @@
           <t>MARTIN Gerome</t>
         </is>
       </c>
-      <c r="U196" t="inlineStr">
+      <c r="X196" t="inlineStr">
         <is>
           <t>36720</t>
         </is>
@@ -11815,7 +11845,7 @@
           <t>CURTIS Samuel</t>
         </is>
       </c>
-      <c r="U197" t="inlineStr">
+      <c r="X197" t="inlineStr">
         <is>
           <t>36683</t>
         </is>
@@ -11873,7 +11903,7 @@
           <t>SOARES Renan</t>
         </is>
       </c>
-      <c r="U198" t="inlineStr">
+      <c r="X198" t="inlineStr">
         <is>
           <t>42776</t>
         </is>
@@ -11931,7 +11961,7 @@
           <t>MIKO Radoslav</t>
         </is>
       </c>
-      <c r="U199" t="inlineStr">
+      <c r="X199" t="inlineStr">
         <is>
           <t>71930</t>
         </is>
@@ -11989,7 +12019,7 @@
           <t>KANAYA Tohru</t>
         </is>
       </c>
-      <c r="U200" t="inlineStr">
+      <c r="X200" t="inlineStr">
         <is>
           <t>36484</t>
         </is>
@@ -12047,7 +12077,7 @@
           <t>YOSHIDA Taku</t>
         </is>
       </c>
-      <c r="U201" t="inlineStr">
+      <c r="X201" t="inlineStr">
         <is>
           <t>41611</t>
         </is>
@@ -12105,7 +12135,7 @@
           <t>MAPELLI Guilherme Marcello</t>
         </is>
       </c>
-      <c r="U202" t="inlineStr">
+      <c r="X202" t="inlineStr">
         <is>
           <t>38015</t>
         </is>
@@ -12163,7 +12193,7 @@
           <t>CHIARELLO Gelindo</t>
         </is>
       </c>
-      <c r="U203" t="inlineStr">
+      <c r="X203" t="inlineStr">
         <is>
           <t>39956</t>
         </is>
@@ -12221,7 +12251,7 @@
           <t>STANOVSKY Martin</t>
         </is>
       </c>
-      <c r="U204" t="inlineStr">
+      <c r="X204" t="inlineStr">
         <is>
           <t>68782</t>
         </is>
@@ -12279,7 +12309,7 @@
           <t>FORD David</t>
         </is>
       </c>
-      <c r="U205" t="inlineStr">
+      <c r="X205" t="inlineStr">
         <is>
           <t>35532</t>
         </is>
@@ -12337,7 +12367,7 @@
           <t>WAHLEN Fredrik</t>
         </is>
       </c>
-      <c r="U206" t="inlineStr">
+      <c r="X206" t="inlineStr">
         <is>
           <t>35102</t>
         </is>
@@ -12395,7 +12425,7 @@
           <t>QUAN Xin</t>
         </is>
       </c>
-      <c r="U207" t="inlineStr">
+      <c r="X207" t="inlineStr">
         <is>
           <t>62343</t>
         </is>
@@ -12453,7 +12483,7 @@
           <t>BOWERS Christopher</t>
         </is>
       </c>
-      <c r="U208" t="inlineStr">
+      <c r="X208" t="inlineStr">
         <is>
           <t>52010</t>
         </is>
@@ -12511,7 +12541,7 @@
           <t>TAYLER Michael</t>
         </is>
       </c>
-      <c r="U209" t="inlineStr">
+      <c r="X209" t="inlineStr">
         <is>
           <t>36262</t>
         </is>
@@ -12569,7 +12599,7 @@
           <t>MACUS Richard</t>
         </is>
       </c>
-      <c r="U210" t="inlineStr">
+      <c r="X210" t="inlineStr">
         <is>
           <t>42855</t>
         </is>
@@ -12627,7 +12657,7 @@
           <t>TRAVOSTINO Benjamin</t>
         </is>
       </c>
-      <c r="U211" t="inlineStr">
+      <c r="X211" t="inlineStr">
         <is>
           <t>68795</t>
         </is>
@@ -12685,7 +12715,7 @@
           <t>DRAPER Warwick</t>
         </is>
       </c>
-      <c r="U212" t="inlineStr">
+      <c r="X212" t="inlineStr">
         <is>
           <t>36536</t>
         </is>
@@ -12743,7 +12773,7 @@
           <t>WEGER Jakob</t>
         </is>
       </c>
-      <c r="U213" t="inlineStr">
+      <c r="X213" t="inlineStr">
         <is>
           <t>54909</t>
         </is>
@@ -12801,7 +12831,7 @@
           <t>PASIUT Michal</t>
         </is>
       </c>
-      <c r="U214" t="inlineStr">
+      <c r="X214" t="inlineStr">
         <is>
           <t>35095</t>
         </is>
@@ -12859,7 +12889,7 @@
           <t>TSVIET Igor</t>
         </is>
       </c>
-      <c r="U215" t="inlineStr">
+      <c r="X215" t="inlineStr">
         <is>
           <t>35527</t>
         </is>
@@ -12917,7 +12947,7 @@
           <t>HOLMER Erik</t>
         </is>
       </c>
-      <c r="U216" t="inlineStr">
+      <c r="X216" t="inlineStr">
         <is>
           <t>35104</t>
         </is>
@@ -12975,7 +13005,7 @@
           <t>BUTCHER Finn</t>
         </is>
       </c>
-      <c r="U217" t="inlineStr">
+      <c r="X217" t="inlineStr">
         <is>
           <t>36663</t>
         </is>
@@ -13033,7 +13063,7 @@
           <t>POTOCNY Marcel</t>
         </is>
       </c>
-      <c r="U218" t="inlineStr">
+      <c r="X218" t="inlineStr">
         <is>
           <t>35235</t>
         </is>
@@ -13091,7 +13121,7 @@
           <t>GILBERT Callum</t>
         </is>
       </c>
-      <c r="U219" t="inlineStr">
+      <c r="X219" t="inlineStr">
         <is>
           <t>42090</t>
         </is>
@@ -13202,7 +13232,7 @@
           <t>DAWSON Mike</t>
         </is>
       </c>
-      <c r="U221" t="inlineStr">
+      <c r="X221" t="inlineStr">
         <is>
           <t>36656</t>
         </is>
@@ -13260,7 +13290,7 @@
           <t>IVALDI Zeno</t>
         </is>
       </c>
-      <c r="U222" t="inlineStr">
+      <c r="X222" t="inlineStr">
         <is>
           <t>35480</t>
         </is>
@@ -13318,7 +13348,7 @@
           <t>OHRSTROM Isak</t>
         </is>
       </c>
-      <c r="U223" t="inlineStr">
+      <c r="X223" t="inlineStr">
         <is>
           <t>35101</t>
         </is>
@@ -13376,7 +13406,7 @@
           <t>EIGEL Pavel</t>
         </is>
       </c>
-      <c r="U224" t="inlineStr">
+      <c r="X224" t="inlineStr">
         <is>
           <t>35458</t>
         </is>
@@ -13434,7 +13464,7 @@
           <t>FORBES-CRYANS Bradley</t>
         </is>
       </c>
-      <c r="U225" t="inlineStr">
+      <c r="X225" t="inlineStr">
         <is>
           <t>36513</t>
         </is>
@@ -13492,7 +13522,7 @@
           <t>CLARKE Joseph</t>
         </is>
       </c>
-      <c r="U226" t="inlineStr">
+      <c r="X226" t="inlineStr">
         <is>
           <t>35654</t>
         </is>
@@ -13550,7 +13580,7 @@
           <t>SMOLEN Michal</t>
         </is>
       </c>
-      <c r="U227" t="inlineStr">
+      <c r="X227" t="inlineStr">
         <is>
           <t>36397</t>
         </is>
@@ -13608,7 +13638,7 @@
           <t>GRIMM Alexander</t>
         </is>
       </c>
-      <c r="U228" t="inlineStr">
+      <c r="X228" t="inlineStr">
         <is>
           <t>35112</t>
         </is>
@@ -13666,7 +13696,7 @@
           <t>BERSINGER Thomas</t>
         </is>
       </c>
-      <c r="U229" t="inlineStr">
+      <c r="X229" t="inlineStr">
         <is>
           <t>35228</t>
         </is>
@@ -13724,7 +13754,7 @@
           <t>GRIGAR Jakub</t>
         </is>
       </c>
-      <c r="U230" t="inlineStr">
+      <c r="X230" t="inlineStr">
         <is>
           <t>37284</t>
         </is>
@@ -13979,7 +14009,7 @@
           <t>PORNCHAI Thatchaporn</t>
         </is>
       </c>
-      <c r="U235" t="inlineStr">
+      <c r="X235" t="inlineStr">
         <is>
           <t>68853</t>
         </is>
@@ -14037,7 +14067,7 @@
           <t>FLEPP Milena</t>
         </is>
       </c>
-      <c r="U236" t="inlineStr">
+      <c r="X236" t="inlineStr">
         <is>
           <t>73274</t>
         </is>
@@ -14201,7 +14231,7 @@
           <t>DAVIS Avery</t>
         </is>
       </c>
-      <c r="U239" t="inlineStr">
+      <c r="X239" t="inlineStr">
         <is>
           <t>71336</t>
         </is>
@@ -14259,7 +14289,7 @@
           <t>MITASIKOVA Monika</t>
         </is>
       </c>
-      <c r="U240" t="inlineStr">
+      <c r="X240" t="inlineStr">
         <is>
           <t>75445</t>
         </is>
@@ -14317,7 +14347,7 @@
           <t>GALUSKOVA Antonie</t>
         </is>
       </c>
-      <c r="U241" t="inlineStr">
+      <c r="X241" t="inlineStr">
         <is>
           <t>68754</t>
         </is>
@@ -14375,7 +14405,7 @@
           <t>BAYLACQ Oceane</t>
         </is>
       </c>
-      <c r="U242" t="inlineStr">
+      <c r="X242" t="inlineStr">
         <is>
           <t>69444</t>
         </is>
@@ -14433,7 +14463,7 @@
           <t>JODAR Celia</t>
         </is>
       </c>
-      <c r="U243" t="inlineStr">
+      <c r="X243" t="inlineStr">
         <is>
           <t>36936</t>
         </is>
@@ -14491,7 +14521,7 @@
           <t>WILLIAMS Courtney</t>
         </is>
       </c>
-      <c r="U244" t="inlineStr">
+      <c r="X244" t="inlineStr">
         <is>
           <t>68771</t>
         </is>
@@ -14549,7 +14579,7 @@
           <t>ESTACIA NETA Omira</t>
         </is>
       </c>
-      <c r="U245" t="inlineStr">
+      <c r="X245" t="inlineStr">
         <is>
           <t>60494</t>
         </is>
@@ -14607,7 +14637,7 @@
           <t>PELLICER CHICA Laura</t>
         </is>
       </c>
-      <c r="U246" t="inlineStr">
+      <c r="X246" t="inlineStr">
         <is>
           <t>43129</t>
         </is>
@@ -14771,7 +14801,7 @@
           <t>ITO Yoshika</t>
         </is>
       </c>
-      <c r="U249" t="inlineStr">
+      <c r="X249" t="inlineStr">
         <is>
           <t>36647</t>
         </is>
@@ -14829,7 +14859,7 @@
           <t>MAHEU Florence</t>
         </is>
       </c>
-      <c r="U250" t="inlineStr">
+      <c r="X250" t="inlineStr">
         <is>
           <t>36416</t>
         </is>
@@ -14887,7 +14917,7 @@
           <t>OROKOCKA Viktoria</t>
         </is>
       </c>
-      <c r="U251" t="inlineStr">
+      <c r="X251" t="inlineStr">
         <is>
           <t>35667</t>
         </is>
@@ -14945,7 +14975,7 @@
           <t>LEENDERS Claudia</t>
         </is>
       </c>
-      <c r="U252" t="inlineStr">
+      <c r="X252" t="inlineStr">
         <is>
           <t>35331</t>
         </is>
@@ -15003,7 +15033,7 @@
           <t>TAKESHITA Yuriko</t>
         </is>
       </c>
-      <c r="U253" t="inlineStr">
+      <c r="X253" t="inlineStr">
         <is>
           <t>36487</t>
         </is>
@@ -15061,7 +15091,7 @@
           <t>MEDON Joanna</t>
         </is>
       </c>
-      <c r="U254" t="inlineStr">
+      <c r="X254" t="inlineStr">
         <is>
           <t>35438</t>
         </is>
@@ -15119,7 +15149,7 @@
           <t>REN Ye</t>
         </is>
       </c>
-      <c r="U255" t="inlineStr">
+      <c r="X255" t="inlineStr">
         <is>
           <t>68810</t>
         </is>
@@ -15177,7 +15207,7 @@
           <t>LI Tong</t>
         </is>
       </c>
-      <c r="U256" t="inlineStr">
+      <c r="X256" t="inlineStr">
         <is>
           <t>52023</t>
         </is>
@@ -15235,7 +15265,7 @@
           <t>YAZAWA Aki</t>
         </is>
       </c>
-      <c r="U257" t="inlineStr">
+      <c r="X257" t="inlineStr">
         <is>
           <t>36486</t>
         </is>
@@ -15293,7 +15323,7 @@
           <t>WERATSCHNIG Nina</t>
         </is>
       </c>
-      <c r="U258" t="inlineStr">
+      <c r="X258" t="inlineStr">
         <is>
           <t>41614</t>
         </is>
@@ -15351,7 +15381,7 @@
           <t>SABATTINI Chiara</t>
         </is>
       </c>
-      <c r="U259" t="inlineStr">
+      <c r="X259" t="inlineStr">
         <is>
           <t>35219</t>
         </is>
@@ -15409,7 +15439,7 @@
           <t>GIAI PRON Maria Clara</t>
         </is>
       </c>
-      <c r="U260" t="inlineStr">
+      <c r="X260" t="inlineStr">
         <is>
           <t>35218</t>
         </is>
@@ -15467,7 +15497,7 @@
           <t>BAUDU Lucie</t>
         </is>
       </c>
-      <c r="U261" t="inlineStr">
+      <c r="X261" t="inlineStr">
         <is>
           <t>35669</t>
         </is>
@@ -15525,7 +15555,7 @@
           <t>NOVAK Ajda</t>
         </is>
       </c>
-      <c r="U262" t="inlineStr">
+      <c r="X262" t="inlineStr">
         <is>
           <t>39079</t>
         </is>
@@ -15583,7 +15613,7 @@
           <t>HILGERTOVA Amalie</t>
         </is>
       </c>
-      <c r="U263" t="inlineStr">
+      <c r="X263" t="inlineStr">
         <is>
           <t>36113</t>
         </is>
@@ -15641,7 +15671,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U264" t="inlineStr">
+      <c r="X264" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -15699,7 +15729,7 @@
           <t>ECKHARDT Kate</t>
         </is>
       </c>
-      <c r="U265" t="inlineStr">
+      <c r="X265" t="inlineStr">
         <is>
           <t>44815</t>
         </is>
@@ -15757,7 +15787,7 @@
           <t>NEVARILOVA Kristina</t>
         </is>
       </c>
-      <c r="U266" t="inlineStr">
+      <c r="X266" t="inlineStr">
         <is>
           <t>35467</t>
         </is>
@@ -15815,7 +15845,7 @@
           <t>WEGMAN Martina</t>
         </is>
       </c>
-      <c r="U267" t="inlineStr">
+      <c r="X267" t="inlineStr">
         <is>
           <t>35345</t>
         </is>
@@ -15873,7 +15903,7 @@
           <t>LAWRENCE Rosalyn</t>
         </is>
       </c>
-      <c r="U268" t="inlineStr">
+      <c r="X268" t="inlineStr">
         <is>
           <t>36531</t>
         </is>
@@ -15931,7 +15961,7 @@
           <t>TROMPETER Caroline</t>
         </is>
       </c>
-      <c r="U269" t="inlineStr">
+      <c r="X269" t="inlineStr">
         <is>
           <t>39167</t>
         </is>
@@ -15989,7 +16019,7 @@
           <t>GOIKOETXEA Irati</t>
         </is>
       </c>
-      <c r="U270" t="inlineStr">
+      <c r="X270" t="inlineStr">
         <is>
           <t>35761</t>
         </is>
@@ -16047,7 +16077,7 @@
           <t>BOUZIDI Carole</t>
         </is>
       </c>
-      <c r="U271" t="inlineStr">
+      <c r="X271" t="inlineStr">
         <is>
           <t>35231</t>
         </is>
@@ -16105,7 +16135,7 @@
           <t>ZWOLINSKA Klaudia</t>
         </is>
       </c>
-      <c r="U272" t="inlineStr">
+      <c r="X272" t="inlineStr">
         <is>
           <t>42027</t>
         </is>
@@ -16163,7 +16193,7 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U273" t="inlineStr">
+      <c r="X273" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -16221,7 +16251,7 @@
           <t>GALUSKOVA Karolina</t>
         </is>
       </c>
-      <c r="U274" t="inlineStr">
+      <c r="X274" t="inlineStr">
         <is>
           <t>37266</t>
         </is>
@@ -16279,7 +16309,7 @@
           <t>PACIERPNIK Natalia</t>
         </is>
       </c>
-      <c r="U275" t="inlineStr">
+      <c r="X275" t="inlineStr">
         <is>
           <t>35077</t>
         </is>
@@ -16337,7 +16367,7 @@
           <t>FRITSCHE Lisa</t>
         </is>
       </c>
-      <c r="U276" t="inlineStr">
+      <c r="X276" t="inlineStr">
         <is>
           <t>39883</t>
         </is>
@@ -16395,7 +16425,7 @@
           <t>JONES Luuka</t>
         </is>
       </c>
-      <c r="U277" t="inlineStr">
+      <c r="X277" t="inlineStr">
         <is>
           <t>36657</t>
         </is>
@@ -16453,7 +16483,7 @@
           <t>LEITNER Lisa</t>
         </is>
       </c>
-      <c r="U278" t="inlineStr">
+      <c r="X278" t="inlineStr">
         <is>
           <t>35305</t>
         </is>
@@ -16511,7 +16541,7 @@
           <t>WOODS Kimberley</t>
         </is>
       </c>
-      <c r="U279" t="inlineStr">
+      <c r="X279" t="inlineStr">
         <is>
           <t>35650</t>
         </is>
@@ -16569,7 +16599,7 @@
           <t>MARTINEZ Marta</t>
         </is>
       </c>
-      <c r="U280" t="inlineStr">
+      <c r="X280" t="inlineStr">
         <is>
           <t>35760</t>
         </is>
@@ -16627,7 +16657,7 @@
           <t>LAFONT Marie-Zelia</t>
         </is>
       </c>
-      <c r="U281" t="inlineStr">
+      <c r="X281" t="inlineStr">
         <is>
           <t>35374</t>
         </is>
@@ -16685,7 +16715,7 @@
           <t>KHARITONOVA Marta</t>
         </is>
       </c>
-      <c r="U282" t="inlineStr">
+      <c r="X282" t="inlineStr">
         <is>
           <t>35257</t>
         </is>
@@ -16743,7 +16773,7 @@
           <t>FRANKLIN Mallory</t>
         </is>
       </c>
-      <c r="U283" t="inlineStr">
+      <c r="X283" t="inlineStr">
         <is>
           <t>35615</t>
         </is>
@@ -16801,7 +16831,7 @@
           <t>HORN Stefanie</t>
         </is>
       </c>
-      <c r="U284" t="inlineStr">
+      <c r="X284" t="inlineStr">
         <is>
           <t>38417</t>
         </is>
@@ -16859,7 +16889,7 @@
           <t>PENNIE Fiona</t>
         </is>
       </c>
-      <c r="U285" t="inlineStr">
+      <c r="X285" t="inlineStr">
         <is>
           <t>35638</t>
         </is>
@@ -16917,7 +16947,7 @@
           <t>SATILA Ana</t>
         </is>
       </c>
-      <c r="U286" t="inlineStr">
+      <c r="X286" t="inlineStr">
         <is>
           <t>35327</t>
         </is>
@@ -16975,7 +17005,7 @@
           <t>SCHORNBERG Jasmin</t>
         </is>
       </c>
-      <c r="U287" t="inlineStr">
+      <c r="X287" t="inlineStr">
         <is>
           <t>35206</t>
         </is>
@@ -17033,7 +17063,7 @@
           <t>KUDEJOVA Katerina</t>
         </is>
       </c>
-      <c r="U288" t="inlineStr">
+      <c r="X288" t="inlineStr">
         <is>
           <t>35034</t>
         </is>
@@ -17091,7 +17121,7 @@
           <t>TERCELJ Eva</t>
         </is>
       </c>
-      <c r="U289" t="inlineStr">
+      <c r="X289" t="inlineStr">
         <is>
           <t>36263</t>
         </is>
@@ -17149,7 +17179,7 @@
           <t>DUKATOVA Jana</t>
         </is>
       </c>
-      <c r="U290" t="inlineStr">
+      <c r="X290" t="inlineStr">
         <is>
           <t>35354</t>
         </is>
@@ -17207,7 +17237,7 @@
           <t>KUHNLE Corinna</t>
         </is>
       </c>
-      <c r="U291" t="inlineStr">
+      <c r="X291" t="inlineStr">
         <is>
           <t>35282</t>
         </is>
@@ -17265,7 +17295,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U292" t="inlineStr">
+      <c r="X292" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -17323,7 +17353,7 @@
           <t>CHOURRAUT Maialen</t>
         </is>
       </c>
-      <c r="U293" t="inlineStr">
+      <c r="X293" t="inlineStr">
         <is>
           <t>35787</t>
         </is>
@@ -17381,7 +17411,7 @@
           <t>FUNK Ricarda</t>
         </is>
       </c>
-      <c r="U294" t="inlineStr">
+      <c r="X294" t="inlineStr">
         <is>
           <t>35122</t>
         </is>
@@ -17439,7 +17469,7 @@
           <t>MAXIMOV Vitaly</t>
         </is>
       </c>
-      <c r="U295" t="inlineStr">
+      <c r="X295" t="inlineStr">
         <is>
           <t>54800</t>
         </is>
@@ -17497,7 +17527,7 @@
           <t>ALVARENGA Frederico</t>
         </is>
       </c>
-      <c r="U296" t="inlineStr">
+      <c r="X296" t="inlineStr">
         <is>
           <t>71976</t>
         </is>
@@ -17555,7 +17585,7 @@
           <t>CHIARELLO Gelindo</t>
         </is>
       </c>
-      <c r="U297" t="inlineStr">
+      <c r="X297" t="inlineStr">
         <is>
           <t>39956</t>
         </is>
@@ -17613,7 +17643,7 @@
           <t>MARZO Daniel</t>
         </is>
       </c>
-      <c r="U298" t="inlineStr">
+      <c r="X298" t="inlineStr">
         <is>
           <t>35757</t>
         </is>
@@ -17671,7 +17701,7 @@
           <t>BOURHIS Yves</t>
         </is>
       </c>
-      <c r="U299" t="inlineStr">
+      <c r="X299" t="inlineStr">
         <is>
           <t>63237</t>
         </is>
@@ -17729,7 +17759,7 @@
           <t>SZCZEPANSKI Piotr</t>
         </is>
       </c>
-      <c r="U300" t="inlineStr">
+      <c r="X300" t="inlineStr">
         <is>
           <t>35080</t>
         </is>
@@ -17787,7 +17817,7 @@
           <t>ZHENG Jiaxin</t>
         </is>
       </c>
-      <c r="U301" t="inlineStr">
+      <c r="X301" t="inlineStr">
         <is>
           <t>75381</t>
         </is>
@@ -17845,7 +17875,7 @@
           <t>DOBY Mathieu</t>
         </is>
       </c>
-      <c r="U302" t="inlineStr">
+      <c r="X302" t="inlineStr">
         <is>
           <t>35292</t>
         </is>
@@ -17903,7 +17933,7 @@
           <t>LONG Tren</t>
         </is>
       </c>
-      <c r="U303" t="inlineStr">
+      <c r="X303" t="inlineStr">
         <is>
           <t>57124</t>
         </is>
@@ -17961,7 +17991,7 @@
           <t>CHAIDET Yutthakan</t>
         </is>
       </c>
-      <c r="U304" t="inlineStr">
+      <c r="X304" t="inlineStr">
         <is>
           <t>51798</t>
         </is>
@@ -18019,7 +18049,7 @@
           <t>HIGGINS Shaun</t>
         </is>
       </c>
-      <c r="U305" t="inlineStr">
+      <c r="X305" t="inlineStr">
         <is>
           <t>36655</t>
         </is>
@@ -18077,7 +18107,7 @@
           <t>SMEDLEY Liam</t>
         </is>
       </c>
-      <c r="U306" t="inlineStr">
+      <c r="X306" t="inlineStr">
         <is>
           <t>36517</t>
         </is>
@@ -18135,7 +18165,7 @@
           <t>COCHRANE Jake</t>
         </is>
       </c>
-      <c r="U307" t="inlineStr">
+      <c r="X307" t="inlineStr">
         <is>
           <t>60124</t>
         </is>
@@ -18193,7 +18223,7 @@
           <t>HENDRICK Robert</t>
         </is>
       </c>
-      <c r="U308" t="inlineStr">
+      <c r="X308" t="inlineStr">
         <is>
           <t>43002</t>
         </is>
@@ -18251,7 +18281,7 @@
           <t>POMEROY Spencer</t>
         </is>
       </c>
-      <c r="U309" t="inlineStr">
+      <c r="X309" t="inlineStr">
         <is>
           <t>57783</t>
         </is>
@@ -18309,7 +18339,7 @@
           <t>SASAKI Shota</t>
         </is>
       </c>
-      <c r="U310" t="inlineStr">
+      <c r="X310" t="inlineStr">
         <is>
           <t>41610</t>
         </is>
@@ -18367,7 +18397,7 @@
           <t>SHU Jianming</t>
         </is>
       </c>
-      <c r="U311" t="inlineStr">
+      <c r="X311" t="inlineStr">
         <is>
           <t>47327</t>
         </is>
@@ -18425,7 +18455,7 @@
           <t>CURCEL Leonardo</t>
         </is>
       </c>
-      <c r="U312" t="inlineStr">
+      <c r="X312" t="inlineStr">
         <is>
           <t>38014</t>
         </is>
@@ -18483,7 +18513,7 @@
           <t>GIBB Benjamin</t>
         </is>
       </c>
-      <c r="U313" t="inlineStr">
+      <c r="X313" t="inlineStr">
         <is>
           <t>36711</t>
         </is>
@@ -18541,7 +18571,7 @@
           <t>CORREA Charles</t>
         </is>
       </c>
-      <c r="U314" t="inlineStr">
+      <c r="X314" t="inlineStr">
         <is>
           <t>38018</t>
         </is>
@@ -18599,7 +18629,7 @@
           <t>SZTUBA Kacper</t>
         </is>
       </c>
-      <c r="U315" t="inlineStr">
+      <c r="X315" t="inlineStr">
         <is>
           <t>53636</t>
         </is>
@@ -18657,7 +18687,7 @@
           <t>TRAVE Miquel</t>
         </is>
       </c>
-      <c r="U316" t="inlineStr">
+      <c r="X316" t="inlineStr">
         <is>
           <t>68998</t>
         </is>
@@ -18715,7 +18745,7 @@
           <t>WATKINS Daniel</t>
         </is>
       </c>
-      <c r="U317" t="inlineStr">
+      <c r="X317" t="inlineStr">
         <is>
           <t>38430</t>
         </is>
@@ -18773,7 +18803,7 @@
           <t>CARTER Tristan</t>
         </is>
       </c>
-      <c r="U318" t="inlineStr">
+      <c r="X318" t="inlineStr">
         <is>
           <t>51890</t>
         </is>
@@ -18831,7 +18861,7 @@
           <t>BORGES Felipe</t>
         </is>
       </c>
-      <c r="U319" t="inlineStr">
+      <c r="X319" t="inlineStr">
         <is>
           <t>38012</t>
         </is>
@@ -18889,7 +18919,7 @@
           <t>BORROWS Ian</t>
         </is>
       </c>
-      <c r="U320" t="inlineStr">
+      <c r="X320" t="inlineStr">
         <is>
           <t>36534</t>
         </is>
@@ -18947,7 +18977,7 @@
           <t>LE RUYET Edern</t>
         </is>
       </c>
-      <c r="U321" t="inlineStr">
+      <c r="X321" t="inlineStr">
         <is>
           <t>35379</t>
         </is>
@@ -19005,7 +19035,7 @@
           <t>CIPRESSI Stefano</t>
         </is>
       </c>
-      <c r="U322" t="inlineStr">
+      <c r="X322" t="inlineStr">
         <is>
           <t>35495</t>
         </is>
@@ -19063,7 +19093,7 @@
           <t>MARC Jonathan</t>
         </is>
       </c>
-      <c r="U323" t="inlineStr">
+      <c r="X323" t="inlineStr">
         <is>
           <t>35388</t>
         </is>
@@ -19121,7 +19151,7 @@
           <t>LOKKEN Zachary</t>
         </is>
       </c>
-      <c r="U324" t="inlineStr">
+      <c r="X324" t="inlineStr">
         <is>
           <t>35069</t>
         </is>
@@ -19179,7 +19209,7 @@
           <t>JEGOU Liam</t>
         </is>
       </c>
-      <c r="U325" t="inlineStr">
+      <c r="X325" t="inlineStr">
         <is>
           <t>35820</t>
         </is>
@@ -19237,7 +19267,7 @@
           <t>SETKIN Kirill</t>
         </is>
       </c>
-      <c r="U326" t="inlineStr">
+      <c r="X326" t="inlineStr">
         <is>
           <t>35457</t>
         </is>
@@ -19295,7 +19325,7 @@
           <t>BETTGE Nico</t>
         </is>
       </c>
-      <c r="U327" t="inlineStr">
+      <c r="X327" t="inlineStr">
         <is>
           <t>35133</t>
         </is>
@@ -19353,7 +19383,7 @@
           <t>CHALOUPKA Vaclav</t>
         </is>
       </c>
-      <c r="U328" t="inlineStr">
+      <c r="X328" t="inlineStr">
         <is>
           <t>51648</t>
         </is>
@@ -19411,7 +19441,7 @@
           <t>MARINIC Matija</t>
         </is>
       </c>
-      <c r="U329" t="inlineStr">
+      <c r="X329" t="inlineStr">
         <is>
           <t>35595</t>
         </is>
@@ -19469,7 +19499,7 @@
           <t>SMEDLEY Cameron</t>
         </is>
       </c>
-      <c r="U330" t="inlineStr">
+      <c r="X330" t="inlineStr">
         <is>
           <t>35543</t>
         </is>
@@ -19527,7 +19557,7 @@
           <t>COLAZINGARI Roberto</t>
         </is>
       </c>
-      <c r="U331" t="inlineStr">
+      <c r="X331" t="inlineStr">
         <is>
           <t>35223</t>
         </is>
@@ -19585,7 +19615,7 @@
           <t>IVALDI Raffaello</t>
         </is>
       </c>
-      <c r="U332" t="inlineStr">
+      <c r="X332" t="inlineStr">
         <is>
           <t>35227</t>
         </is>
@@ -19643,7 +19673,7 @@
           <t>JANE Michal</t>
         </is>
       </c>
-      <c r="U333" t="inlineStr">
+      <c r="X333" t="inlineStr">
         <is>
           <t>35059</t>
         </is>
@@ -19701,7 +19731,7 @@
           <t>BADURA Jergus</t>
         </is>
       </c>
-      <c r="U334" t="inlineStr">
+      <c r="X334" t="inlineStr">
         <is>
           <t>68767</t>
         </is>
@@ -19759,7 +19789,7 @@
           <t>LENARCIC Jure</t>
         </is>
       </c>
-      <c r="U335" t="inlineStr">
+      <c r="X335" t="inlineStr">
         <is>
           <t>36259</t>
         </is>
@@ -19817,7 +19847,7 @@
           <t>HEDWIG Grzegorz</t>
         </is>
       </c>
-      <c r="U336" t="inlineStr">
+      <c r="X336" t="inlineStr">
         <is>
           <t>35465</t>
         </is>
@@ -19875,7 +19905,7 @@
           <t>THOMAS Martin</t>
         </is>
       </c>
-      <c r="U337" t="inlineStr">
+      <c r="X337" t="inlineStr">
         <is>
           <t>35412</t>
         </is>
@@ -19933,7 +19963,7 @@
           <t>GEBAS Vitezslav</t>
         </is>
       </c>
-      <c r="U338" t="inlineStr">
+      <c r="X338" t="inlineStr">
         <is>
           <t>35038</t>
         </is>
@@ -19991,7 +20021,7 @@
           <t>BOZIC Luka</t>
         </is>
       </c>
-      <c r="U339" t="inlineStr">
+      <c r="X339" t="inlineStr">
         <is>
           <t>36269</t>
         </is>
@@ -20049,7 +20079,7 @@
           <t>ELOSEGI Ander</t>
         </is>
       </c>
-      <c r="U340" t="inlineStr">
+      <c r="X340" t="inlineStr">
         <is>
           <t>35785</t>
         </is>
@@ -20107,7 +20137,7 @@
           <t>EICHFELD Casey</t>
         </is>
       </c>
-      <c r="U341" t="inlineStr">
+      <c r="X341" t="inlineStr">
         <is>
           <t>35067</t>
         </is>
@@ -20165,7 +20195,7 @@
           <t>BERCIC Anze</t>
         </is>
       </c>
-      <c r="U342" t="inlineStr">
+      <c r="X342" t="inlineStr">
         <is>
           <t>36253</t>
         </is>
@@ -20223,7 +20253,7 @@
           <t>HANEDA Takuya</t>
         </is>
       </c>
-      <c r="U343" t="inlineStr">
+      <c r="X343" t="inlineStr">
         <is>
           <t>36481</t>
         </is>
@@ -20281,7 +20311,7 @@
           <t>BURGESS Adam</t>
         </is>
       </c>
-      <c r="U344" t="inlineStr">
+      <c r="X344" t="inlineStr">
         <is>
           <t>35647</t>
         </is>
@@ -20339,7 +20369,7 @@
           <t>MARTIKAN Michal</t>
         </is>
       </c>
-      <c r="U345" t="inlineStr">
+      <c r="X345" t="inlineStr">
         <is>
           <t>35365</t>
         </is>
@@ -20397,7 +20427,7 @@
           <t>FLORENCE David</t>
         </is>
       </c>
-      <c r="U346" t="inlineStr">
+      <c r="X346" t="inlineStr">
         <is>
           <t>35634</t>
         </is>
@@ -20455,7 +20485,7 @@
           <t>ANTON Franz</t>
         </is>
       </c>
-      <c r="U347" t="inlineStr">
+      <c r="X347" t="inlineStr">
         <is>
           <t>35137</t>
         </is>
@@ -20513,7 +20543,7 @@
           <t>WESTLEY Ryan</t>
         </is>
       </c>
-      <c r="U348" t="inlineStr">
+      <c r="X348" t="inlineStr">
         <is>
           <t>35651</t>
         </is>
@@ -20571,7 +20601,7 @@
           <t>TASIADIS Sideris</t>
         </is>
       </c>
-      <c r="U349" t="inlineStr">
+      <c r="X349" t="inlineStr">
         <is>
           <t>35135</t>
         </is>
@@ -20629,7 +20659,7 @@
           <t>SLAFKOVSKY Alexander</t>
         </is>
       </c>
-      <c r="U350" t="inlineStr">
+      <c r="X350" t="inlineStr">
         <is>
           <t>35129</t>
         </is>
@@ -20687,7 +20717,7 @@
           <t>GARGAUD CHANUT Denis</t>
         </is>
       </c>
-      <c r="U351" t="inlineStr">
+      <c r="X351" t="inlineStr">
         <is>
           <t>35177</t>
         </is>
@@ -20745,7 +20775,7 @@
           <t>SAVSEK Benjamin</t>
         </is>
       </c>
-      <c r="U352" t="inlineStr">
+      <c r="X352" t="inlineStr">
         <is>
           <t>36218</t>
         </is>
@@ -20803,7 +20833,7 @@
           <t>BENUS Matej</t>
         </is>
       </c>
-      <c r="U353" t="inlineStr">
+      <c r="X353" t="inlineStr">
         <is>
           <t>35353</t>
         </is>
@@ -20861,7 +20891,7 @@
           <t>PORNCHAI Thatchaporn</t>
         </is>
       </c>
-      <c r="U354" t="inlineStr">
+      <c r="X354" t="inlineStr">
         <is>
           <t>68853</t>
         </is>
@@ -20919,7 +20949,7 @@
           <t>FLEPP Milena</t>
         </is>
       </c>
-      <c r="U355" t="inlineStr">
+      <c r="X355" t="inlineStr">
         <is>
           <t>73274</t>
         </is>
@@ -21083,7 +21113,7 @@
           <t>DAVIS Avery</t>
         </is>
       </c>
-      <c r="U358" t="inlineStr">
+      <c r="X358" t="inlineStr">
         <is>
           <t>71336</t>
         </is>
@@ -21141,7 +21171,7 @@
           <t>MITASIKOVA Monika</t>
         </is>
       </c>
-      <c r="U359" t="inlineStr">
+      <c r="X359" t="inlineStr">
         <is>
           <t>75445</t>
         </is>
@@ -21199,7 +21229,7 @@
           <t>GALUSKOVA Antonie</t>
         </is>
       </c>
-      <c r="U360" t="inlineStr">
+      <c r="X360" t="inlineStr">
         <is>
           <t>68754</t>
         </is>
@@ -21257,7 +21287,7 @@
           <t>BAYLACQ Oceane</t>
         </is>
       </c>
-      <c r="U361" t="inlineStr">
+      <c r="X361" t="inlineStr">
         <is>
           <t>69444</t>
         </is>
@@ -21315,7 +21345,7 @@
           <t>JODAR Celia</t>
         </is>
       </c>
-      <c r="U362" t="inlineStr">
+      <c r="X362" t="inlineStr">
         <is>
           <t>36936</t>
         </is>
@@ -21373,7 +21403,7 @@
           <t>WILLIAMS Courtney</t>
         </is>
       </c>
-      <c r="U363" t="inlineStr">
+      <c r="X363" t="inlineStr">
         <is>
           <t>68771</t>
         </is>
@@ -21431,7 +21461,7 @@
           <t>ESTACIA NETA Omira</t>
         </is>
       </c>
-      <c r="U364" t="inlineStr">
+      <c r="X364" t="inlineStr">
         <is>
           <t>60494</t>
         </is>
@@ -21489,7 +21519,7 @@
           <t>PELLICER CHICA Laura</t>
         </is>
       </c>
-      <c r="U365" t="inlineStr">
+      <c r="X365" t="inlineStr">
         <is>
           <t>43129</t>
         </is>
@@ -21653,7 +21683,7 @@
           <t>ITO Yoshika</t>
         </is>
       </c>
-      <c r="U368" t="inlineStr">
+      <c r="X368" t="inlineStr">
         <is>
           <t>36647</t>
         </is>
@@ -21711,7 +21741,7 @@
           <t>MAHEU Florence</t>
         </is>
       </c>
-      <c r="U369" t="inlineStr">
+      <c r="X369" t="inlineStr">
         <is>
           <t>36416</t>
         </is>
@@ -21769,7 +21799,7 @@
           <t>OROKOCKA Viktoria</t>
         </is>
       </c>
-      <c r="U370" t="inlineStr">
+      <c r="X370" t="inlineStr">
         <is>
           <t>35667</t>
         </is>
@@ -21827,7 +21857,7 @@
           <t>LEENDERS Claudia</t>
         </is>
       </c>
-      <c r="U371" t="inlineStr">
+      <c r="X371" t="inlineStr">
         <is>
           <t>35331</t>
         </is>
@@ -21885,7 +21915,7 @@
           <t>TAKESHITA Yuriko</t>
         </is>
       </c>
-      <c r="U372" t="inlineStr">
+      <c r="X372" t="inlineStr">
         <is>
           <t>36487</t>
         </is>
@@ -21943,7 +21973,7 @@
           <t>MEDON Joanna</t>
         </is>
       </c>
-      <c r="U373" t="inlineStr">
+      <c r="X373" t="inlineStr">
         <is>
           <t>35438</t>
         </is>
@@ -22001,7 +22031,7 @@
           <t>REN Ye</t>
         </is>
       </c>
-      <c r="U374" t="inlineStr">
+      <c r="X374" t="inlineStr">
         <is>
           <t>68810</t>
         </is>
@@ -22059,7 +22089,7 @@
           <t>LI Tong</t>
         </is>
       </c>
-      <c r="U375" t="inlineStr">
+      <c r="X375" t="inlineStr">
         <is>
           <t>52023</t>
         </is>
@@ -22117,7 +22147,7 @@
           <t>YAZAWA Aki</t>
         </is>
       </c>
-      <c r="U376" t="inlineStr">
+      <c r="X376" t="inlineStr">
         <is>
           <t>36486</t>
         </is>
@@ -22175,7 +22205,7 @@
           <t>WERATSCHNIG Nina</t>
         </is>
       </c>
-      <c r="U377" t="inlineStr">
+      <c r="X377" t="inlineStr">
         <is>
           <t>41614</t>
         </is>
@@ -22233,7 +22263,7 @@
           <t>BAUDU Lucie</t>
         </is>
       </c>
-      <c r="U378" t="inlineStr">
+      <c r="X378" t="inlineStr">
         <is>
           <t>35669</t>
         </is>
@@ -22291,7 +22321,7 @@
           <t>NOVAK Ajda</t>
         </is>
       </c>
-      <c r="U379" t="inlineStr">
+      <c r="X379" t="inlineStr">
         <is>
           <t>39079</t>
         </is>
@@ -22349,7 +22379,7 @@
           <t>HILGERTOVA Amalie</t>
         </is>
       </c>
-      <c r="U380" t="inlineStr">
+      <c r="X380" t="inlineStr">
         <is>
           <t>36113</t>
         </is>
@@ -22407,7 +22437,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U381" t="inlineStr">
+      <c r="X381" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -22465,7 +22495,7 @@
           <t>NEVARILOVA Kristina</t>
         </is>
       </c>
-      <c r="U382" t="inlineStr">
+      <c r="X382" t="inlineStr">
         <is>
           <t>35467</t>
         </is>
@@ -22523,7 +22553,7 @@
           <t>WEGMAN Martina</t>
         </is>
       </c>
-      <c r="U383" t="inlineStr">
+      <c r="X383" t="inlineStr">
         <is>
           <t>35345</t>
         </is>
@@ -22581,7 +22611,7 @@
           <t>LAWRENCE Rosalyn</t>
         </is>
       </c>
-      <c r="U384" t="inlineStr">
+      <c r="X384" t="inlineStr">
         <is>
           <t>36531</t>
         </is>
@@ -22639,7 +22669,7 @@
           <t>TROMPETER Caroline</t>
         </is>
       </c>
-      <c r="U385" t="inlineStr">
+      <c r="X385" t="inlineStr">
         <is>
           <t>39167</t>
         </is>
@@ -22697,7 +22727,7 @@
           <t>GOIKOETXEA Irati</t>
         </is>
       </c>
-      <c r="U386" t="inlineStr">
+      <c r="X386" t="inlineStr">
         <is>
           <t>35761</t>
         </is>
@@ -22755,7 +22785,7 @@
           <t>ZWOLINSKA Klaudia</t>
         </is>
       </c>
-      <c r="U387" t="inlineStr">
+      <c r="X387" t="inlineStr">
         <is>
           <t>42027</t>
         </is>
@@ -22813,7 +22843,7 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U388" t="inlineStr">
+      <c r="X388" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -22871,7 +22901,7 @@
           <t>GALUSKOVA Karolina</t>
         </is>
       </c>
-      <c r="U389" t="inlineStr">
+      <c r="X389" t="inlineStr">
         <is>
           <t>37266</t>
         </is>
@@ -22929,7 +22959,7 @@
           <t>FRITSCHE Lisa</t>
         </is>
       </c>
-      <c r="U390" t="inlineStr">
+      <c r="X390" t="inlineStr">
         <is>
           <t>39883</t>
         </is>
@@ -22987,7 +23017,7 @@
           <t>JONES Luuka</t>
         </is>
       </c>
-      <c r="U391" t="inlineStr">
+      <c r="X391" t="inlineStr">
         <is>
           <t>36657</t>
         </is>
@@ -23045,7 +23075,7 @@
           <t>LEITNER Lisa</t>
         </is>
       </c>
-      <c r="U392" t="inlineStr">
+      <c r="X392" t="inlineStr">
         <is>
           <t>35305</t>
         </is>
@@ -23103,7 +23133,7 @@
           <t>KHARITONOVA Marta</t>
         </is>
       </c>
-      <c r="U393" t="inlineStr">
+      <c r="X393" t="inlineStr">
         <is>
           <t>35257</t>
         </is>
@@ -23161,7 +23191,7 @@
           <t>HORN Stefanie</t>
         </is>
       </c>
-      <c r="U394" t="inlineStr">
+      <c r="X394" t="inlineStr">
         <is>
           <t>38417</t>
         </is>
@@ -23219,7 +23249,7 @@
           <t>MAXIMOV Vitaly</t>
         </is>
       </c>
-      <c r="U395" t="inlineStr">
+      <c r="X395" t="inlineStr">
         <is>
           <t>54800</t>
         </is>
@@ -23277,7 +23307,7 @@
           <t>ALVARENGA Frederico</t>
         </is>
       </c>
-      <c r="U396" t="inlineStr">
+      <c r="X396" t="inlineStr">
         <is>
           <t>71976</t>
         </is>
@@ -23335,7 +23365,7 @@
           <t>CHIARELLO Gelindo</t>
         </is>
       </c>
-      <c r="U397" t="inlineStr">
+      <c r="X397" t="inlineStr">
         <is>
           <t>39956</t>
         </is>
@@ -23393,7 +23423,7 @@
           <t>MARZO Daniel</t>
         </is>
       </c>
-      <c r="U398" t="inlineStr">
+      <c r="X398" t="inlineStr">
         <is>
           <t>35757</t>
         </is>
@@ -23451,7 +23481,7 @@
           <t>BOURHIS Yves</t>
         </is>
       </c>
-      <c r="U399" t="inlineStr">
+      <c r="X399" t="inlineStr">
         <is>
           <t>63237</t>
         </is>
@@ -23509,7 +23539,7 @@
           <t>SZCZEPANSKI Piotr</t>
         </is>
       </c>
-      <c r="U400" t="inlineStr">
+      <c r="X400" t="inlineStr">
         <is>
           <t>35080</t>
         </is>
@@ -23567,7 +23597,7 @@
           <t>ZHENG Jiaxin</t>
         </is>
       </c>
-      <c r="U401" t="inlineStr">
+      <c r="X401" t="inlineStr">
         <is>
           <t>75381</t>
         </is>
@@ -23625,7 +23655,7 @@
           <t>DOBY Mathieu</t>
         </is>
       </c>
-      <c r="U402" t="inlineStr">
+      <c r="X402" t="inlineStr">
         <is>
           <t>35292</t>
         </is>
@@ -23683,7 +23713,7 @@
           <t>LONG Tren</t>
         </is>
       </c>
-      <c r="U403" t="inlineStr">
+      <c r="X403" t="inlineStr">
         <is>
           <t>57124</t>
         </is>
@@ -23741,7 +23771,7 @@
           <t>CHAIDET Yutthakan</t>
         </is>
       </c>
-      <c r="U404" t="inlineStr">
+      <c r="X404" t="inlineStr">
         <is>
           <t>51798</t>
         </is>
@@ -23799,7 +23829,7 @@
           <t>HIGGINS Shaun</t>
         </is>
       </c>
-      <c r="U405" t="inlineStr">
+      <c r="X405" t="inlineStr">
         <is>
           <t>36655</t>
         </is>
@@ -23857,7 +23887,7 @@
           <t>SMEDLEY Liam</t>
         </is>
       </c>
-      <c r="U406" t="inlineStr">
+      <c r="X406" t="inlineStr">
         <is>
           <t>36517</t>
         </is>
@@ -23915,7 +23945,7 @@
           <t>COCHRANE Jake</t>
         </is>
       </c>
-      <c r="U407" t="inlineStr">
+      <c r="X407" t="inlineStr">
         <is>
           <t>60124</t>
         </is>
@@ -23973,7 +24003,7 @@
           <t>HENDRICK Robert</t>
         </is>
       </c>
-      <c r="U408" t="inlineStr">
+      <c r="X408" t="inlineStr">
         <is>
           <t>43002</t>
         </is>
@@ -24031,7 +24061,7 @@
           <t>POMEROY Spencer</t>
         </is>
       </c>
-      <c r="U409" t="inlineStr">
+      <c r="X409" t="inlineStr">
         <is>
           <t>57783</t>
         </is>
@@ -24089,7 +24119,7 @@
           <t>SASAKI Shota</t>
         </is>
       </c>
-      <c r="U410" t="inlineStr">
+      <c r="X410" t="inlineStr">
         <is>
           <t>41610</t>
         </is>
@@ -24147,7 +24177,7 @@
           <t>SHU Jianming</t>
         </is>
       </c>
-      <c r="U411" t="inlineStr">
+      <c r="X411" t="inlineStr">
         <is>
           <t>47327</t>
         </is>
@@ -24205,7 +24235,7 @@
           <t>CURCEL Leonardo</t>
         </is>
       </c>
-      <c r="U412" t="inlineStr">
+      <c r="X412" t="inlineStr">
         <is>
           <t>38014</t>
         </is>
@@ -24263,7 +24293,7 @@
           <t>GIBB Benjamin</t>
         </is>
       </c>
-      <c r="U413" t="inlineStr">
+      <c r="X413" t="inlineStr">
         <is>
           <t>36711</t>
         </is>
@@ -24321,7 +24351,7 @@
           <t>CORREA Charles</t>
         </is>
       </c>
-      <c r="U414" t="inlineStr">
+      <c r="X414" t="inlineStr">
         <is>
           <t>38018</t>
         </is>
@@ -24379,7 +24409,7 @@
           <t>SZTUBA Kacper</t>
         </is>
       </c>
-      <c r="U415" t="inlineStr">
+      <c r="X415" t="inlineStr">
         <is>
           <t>53636</t>
         </is>
@@ -24437,7 +24467,7 @@
           <t>TRAVE Miquel</t>
         </is>
       </c>
-      <c r="U416" t="inlineStr">
+      <c r="X416" t="inlineStr">
         <is>
           <t>68998</t>
         </is>
@@ -24495,7 +24525,7 @@
           <t>WATKINS Daniel</t>
         </is>
       </c>
-      <c r="U417" t="inlineStr">
+      <c r="X417" t="inlineStr">
         <is>
           <t>38430</t>
         </is>
@@ -24553,7 +24583,7 @@
           <t>CARTER Tristan</t>
         </is>
       </c>
-      <c r="U418" t="inlineStr">
+      <c r="X418" t="inlineStr">
         <is>
           <t>51890</t>
         </is>
@@ -24611,7 +24641,7 @@
           <t>BORGES Felipe</t>
         </is>
       </c>
-      <c r="U419" t="inlineStr">
+      <c r="X419" t="inlineStr">
         <is>
           <t>38012</t>
         </is>
@@ -24669,7 +24699,7 @@
           <t>BORROWS Ian</t>
         </is>
       </c>
-      <c r="U420" t="inlineStr">
+      <c r="X420" t="inlineStr">
         <is>
           <t>36534</t>
         </is>
@@ -24727,7 +24757,7 @@
           <t>LE RUYET Edern</t>
         </is>
       </c>
-      <c r="U421" t="inlineStr">
+      <c r="X421" t="inlineStr">
         <is>
           <t>35379</t>
         </is>
@@ -24785,7 +24815,7 @@
           <t>MARC Jonathan</t>
         </is>
       </c>
-      <c r="U422" t="inlineStr">
+      <c r="X422" t="inlineStr">
         <is>
           <t>35388</t>
         </is>
@@ -24843,7 +24873,7 @@
           <t>LOKKEN Zachary</t>
         </is>
       </c>
-      <c r="U423" t="inlineStr">
+      <c r="X423" t="inlineStr">
         <is>
           <t>35069</t>
         </is>
@@ -24901,7 +24931,7 @@
           <t>JEGOU Liam</t>
         </is>
       </c>
-      <c r="U424" t="inlineStr">
+      <c r="X424" t="inlineStr">
         <is>
           <t>35820</t>
         </is>
@@ -24959,7 +24989,7 @@
           <t>BETTGE Nico</t>
         </is>
       </c>
-      <c r="U425" t="inlineStr">
+      <c r="X425" t="inlineStr">
         <is>
           <t>35133</t>
         </is>
@@ -25017,7 +25047,7 @@
           <t>CHALOUPKA Vaclav</t>
         </is>
       </c>
-      <c r="U426" t="inlineStr">
+      <c r="X426" t="inlineStr">
         <is>
           <t>51648</t>
         </is>
@@ -25075,7 +25105,7 @@
           <t>MARINIC Matija</t>
         </is>
       </c>
-      <c r="U427" t="inlineStr">
+      <c r="X427" t="inlineStr">
         <is>
           <t>35595</t>
         </is>
@@ -25133,7 +25163,7 @@
           <t>JANE Michal</t>
         </is>
       </c>
-      <c r="U428" t="inlineStr">
+      <c r="X428" t="inlineStr">
         <is>
           <t>35059</t>
         </is>
@@ -25191,7 +25221,7 @@
           <t>LENARCIC Jure</t>
         </is>
       </c>
-      <c r="U429" t="inlineStr">
+      <c r="X429" t="inlineStr">
         <is>
           <t>36259</t>
         </is>
@@ -25249,7 +25279,7 @@
           <t>HEDWIG Grzegorz</t>
         </is>
       </c>
-      <c r="U430" t="inlineStr">
+      <c r="X430" t="inlineStr">
         <is>
           <t>35465</t>
         </is>
@@ -25307,7 +25337,7 @@
           <t>GEBAS Vitezslav</t>
         </is>
       </c>
-      <c r="U431" t="inlineStr">
+      <c r="X431" t="inlineStr">
         <is>
           <t>35038</t>
         </is>
@@ -25365,7 +25395,7 @@
           <t>BOZIC Luka</t>
         </is>
       </c>
-      <c r="U432" t="inlineStr">
+      <c r="X432" t="inlineStr">
         <is>
           <t>36269</t>
         </is>
@@ -25423,7 +25453,7 @@
           <t>HANEDA Takuya</t>
         </is>
       </c>
-      <c r="U433" t="inlineStr">
+      <c r="X433" t="inlineStr">
         <is>
           <t>36481</t>
         </is>
@@ -25481,7 +25511,7 @@
           <t>GARGAUD CHANUT Denis</t>
         </is>
       </c>
-      <c r="U434" t="inlineStr">
+      <c r="X434" t="inlineStr">
         <is>
           <t>35177</t>
         </is>
@@ -25799,12 +25829,12 @@
           <t>BETTGE Nico</t>
         </is>
       </c>
-      <c r="U440" t="inlineStr">
+      <c r="X440" t="inlineStr">
         <is>
           <t>35145</t>
         </is>
       </c>
-      <c r="V440" t="inlineStr">
+      <c r="Y440" t="inlineStr">
         <is>
           <t>35133</t>
         </is>
@@ -25867,12 +25897,12 @@
           <t>BATIK Jan</t>
         </is>
       </c>
-      <c r="U441" t="inlineStr">
+      <c r="X441" t="inlineStr">
         <is>
           <t>35368</t>
         </is>
       </c>
-      <c r="V441" t="inlineStr">
+      <c r="Y441" t="inlineStr">
         <is>
           <t>35367</t>
         </is>
@@ -25935,12 +25965,12 @@
           <t>VRZAN Jakub</t>
         </is>
       </c>
-      <c r="U442" t="inlineStr">
+      <c r="X442" t="inlineStr">
         <is>
           <t>35042</t>
         </is>
       </c>
-      <c r="V442" t="inlineStr">
+      <c r="Y442" t="inlineStr">
         <is>
           <t>35043</t>
         </is>
@@ -26003,12 +26033,12 @@
           <t>CAILHOL Hugo</t>
         </is>
       </c>
-      <c r="U443" t="inlineStr">
+      <c r="X443" t="inlineStr">
         <is>
           <t>35476</t>
         </is>
       </c>
-      <c r="V443" t="inlineStr">
+      <c r="Y443" t="inlineStr">
         <is>
           <t>35491</t>
         </is>
@@ -26071,12 +26101,12 @@
           <t>SKANTAR Peter</t>
         </is>
       </c>
-      <c r="U444" t="inlineStr">
+      <c r="X444" t="inlineStr">
         <is>
           <t>35360</t>
         </is>
       </c>
-      <c r="V444" t="inlineStr">
+      <c r="Y444" t="inlineStr">
         <is>
           <t>35361</t>
         </is>
@@ -26139,12 +26169,12 @@
           <t>PEREZ Jesus</t>
         </is>
       </c>
-      <c r="U445" t="inlineStr">
+      <c r="X445" t="inlineStr">
         <is>
           <t>35757</t>
         </is>
       </c>
-      <c r="V445" t="inlineStr">
+      <c r="Y445" t="inlineStr">
         <is>
           <t>36091</t>
         </is>
@@ -26207,12 +26237,12 @@
           <t>CAMPORESI Pietro</t>
         </is>
       </c>
-      <c r="U446" t="inlineStr">
+      <c r="X446" t="inlineStr">
         <is>
           <t>35498</t>
         </is>
       </c>
-      <c r="V446" t="inlineStr">
+      <c r="Y446" t="inlineStr">
         <is>
           <t>35497</t>
         </is>
@@ -26275,12 +26305,12 @@
           <t>BISO Hugo</t>
         </is>
       </c>
-      <c r="U447" t="inlineStr">
+      <c r="X447" t="inlineStr">
         <is>
           <t>35403</t>
         </is>
       </c>
-      <c r="V447" t="inlineStr">
+      <c r="Y447" t="inlineStr">
         <is>
           <t>35229</t>
         </is>
@@ -26343,12 +26373,12 @@
           <t>HOCHSCHORNER Peter</t>
         </is>
       </c>
-      <c r="U448" t="inlineStr">
+      <c r="X448" t="inlineStr">
         <is>
           <t>35356</t>
         </is>
       </c>
-      <c r="V448" t="inlineStr">
+      <c r="Y448" t="inlineStr">
         <is>
           <t>35357</t>
         </is>
@@ -26411,12 +26441,12 @@
           <t>GEWISSLER Matus</t>
         </is>
       </c>
-      <c r="U449" t="inlineStr">
+      <c r="X449" t="inlineStr">
         <is>
           <t>39248</t>
         </is>
       </c>
-      <c r="V449" t="inlineStr">
+      <c r="Y449" t="inlineStr">
         <is>
           <t>39249</t>
         </is>
@@ -26479,12 +26509,12 @@
           <t>JANE Jakub</t>
         </is>
       </c>
-      <c r="U450" t="inlineStr">
+      <c r="X450" t="inlineStr">
         <is>
           <t>35060</t>
         </is>
       </c>
-      <c r="V450" t="inlineStr">
+      <c r="Y450" t="inlineStr">
         <is>
           <t>35061</t>
         </is>
@@ -26547,12 +26577,12 @@
           <t>BECKER Thomas</t>
         </is>
       </c>
-      <c r="U451" t="inlineStr">
+      <c r="X451" t="inlineStr">
         <is>
           <t>35139</t>
         </is>
       </c>
-      <c r="V451" t="inlineStr">
+      <c r="Y451" t="inlineStr">
         <is>
           <t>35143</t>
         </is>
@@ -26615,12 +26645,12 @@
           <t>SINDLER Marek</t>
         </is>
       </c>
-      <c r="U452" t="inlineStr">
+      <c r="X452" t="inlineStr">
         <is>
           <t>35062</t>
         </is>
       </c>
-      <c r="V452" t="inlineStr">
+      <c r="Y452" t="inlineStr">
         <is>
           <t>35063</t>
         </is>
@@ -26683,12 +26713,12 @@
           <t>PECHE Matthieu</t>
         </is>
       </c>
-      <c r="U453" t="inlineStr">
+      <c r="X453" t="inlineStr">
         <is>
           <t>35350</t>
         </is>
       </c>
-      <c r="V453" t="inlineStr">
+      <c r="Y453" t="inlineStr">
         <is>
           <t>35400</t>
         </is>
@@ -26746,7 +26776,7 @@
           <t>BIZJAK Nina</t>
         </is>
       </c>
-      <c r="U454" t="inlineStr">
+      <c r="X454" t="inlineStr">
         <is>
           <t>39984</t>
         </is>
@@ -26804,7 +26834,7 @@
           <t>CHEN Shi</t>
         </is>
       </c>
-      <c r="U455" t="inlineStr">
+      <c r="X455" t="inlineStr">
         <is>
           <t>52027</t>
         </is>
@@ -26862,7 +26892,7 @@
           <t>MACEKOVA Simona</t>
         </is>
       </c>
-      <c r="U456" t="inlineStr">
+      <c r="X456" t="inlineStr">
         <is>
           <t>45153</t>
         </is>
@@ -26920,7 +26950,7 @@
           <t>WOODS Kimberley</t>
         </is>
       </c>
-      <c r="U457" t="inlineStr">
+      <c r="X457" t="inlineStr">
         <is>
           <t>35650</t>
         </is>
@@ -26978,7 +27008,7 @@
           <t>HAVLICKOVA Katerina</t>
         </is>
       </c>
-      <c r="U458" t="inlineStr">
+      <c r="X458" t="inlineStr">
         <is>
           <t>35048</t>
         </is>
@@ -27036,7 +27066,7 @@
           <t>FORROW Bethan</t>
         </is>
       </c>
-      <c r="U459" t="inlineStr">
+      <c r="X459" t="inlineStr">
         <is>
           <t>69065</t>
         </is>
@@ -27094,7 +27124,7 @@
           <t>STANOVSKA Sona</t>
         </is>
       </c>
-      <c r="U460" t="inlineStr">
+      <c r="X460" t="inlineStr">
         <is>
           <t>51647</t>
         </is>
@@ -27152,7 +27182,7 @@
           <t>JONES Luuka</t>
         </is>
       </c>
-      <c r="U461" t="inlineStr">
+      <c r="X461" t="inlineStr">
         <is>
           <t>36657</t>
         </is>
@@ -27210,7 +27240,7 @@
           <t>WERATSCHNIG Nadine</t>
         </is>
       </c>
-      <c r="U462" t="inlineStr">
+      <c r="X462" t="inlineStr">
         <is>
           <t>41613</t>
         </is>
@@ -27268,7 +27298,7 @@
           <t>SATILA Ana</t>
         </is>
       </c>
-      <c r="U463" t="inlineStr">
+      <c r="X463" t="inlineStr">
         <is>
           <t>35327</t>
         </is>
@@ -27326,7 +27356,7 @@
           <t>SABITOVA Zulfia</t>
         </is>
       </c>
-      <c r="U464" t="inlineStr">
+      <c r="X464" t="inlineStr">
         <is>
           <t>40572</t>
         </is>
@@ -27384,7 +27414,7 @@
           <t>PRIOUX Lucie</t>
         </is>
       </c>
-      <c r="U465" t="inlineStr">
+      <c r="X465" t="inlineStr">
         <is>
           <t>42984</t>
         </is>
@@ -27442,7 +27472,7 @@
           <t>JANCOVA Monika</t>
         </is>
       </c>
-      <c r="U466" t="inlineStr">
+      <c r="X466" t="inlineStr">
         <is>
           <t>36015</t>
         </is>
@@ -27500,7 +27530,7 @@
           <t>STOECKLIN Lena</t>
         </is>
       </c>
-      <c r="U467" t="inlineStr">
+      <c r="X467" t="inlineStr">
         <is>
           <t>35822</t>
         </is>
@@ -27558,7 +27588,7 @@
           <t>TIXIER Cecile</t>
         </is>
       </c>
-      <c r="U468" t="inlineStr">
+      <c r="X468" t="inlineStr">
         <is>
           <t>35687</t>
         </is>
@@ -27616,7 +27646,7 @@
           <t>LAWRENCE Rosalyn</t>
         </is>
       </c>
-      <c r="U469" t="inlineStr">
+      <c r="X469" t="inlineStr">
         <is>
           <t>36531</t>
         </is>
@@ -27674,7 +27704,7 @@
           <t>BREGAZZI Ella</t>
         </is>
       </c>
-      <c r="U470" t="inlineStr">
+      <c r="X470" t="inlineStr">
         <is>
           <t>41598</t>
         </is>
@@ -27732,7 +27762,7 @@
           <t>FOX Noemie</t>
         </is>
       </c>
-      <c r="U471" t="inlineStr">
+      <c r="X471" t="inlineStr">
         <is>
           <t>44812</t>
         </is>
@@ -27843,7 +27873,7 @@
           <t>JACQUET Claire</t>
         </is>
       </c>
-      <c r="U473" t="inlineStr">
+      <c r="X473" t="inlineStr">
         <is>
           <t>35684</t>
         </is>
@@ -27901,7 +27931,7 @@
           <t>MUKHGALEEVA Polina</t>
         </is>
       </c>
-      <c r="U474" t="inlineStr">
+      <c r="X474" t="inlineStr">
         <is>
           <t>35768</t>
         </is>
@@ -27959,7 +27989,7 @@
           <t>VAN DER KNIJFF Annebel</t>
         </is>
       </c>
-      <c r="U475" t="inlineStr">
+      <c r="X475" t="inlineStr">
         <is>
           <t>39945</t>
         </is>
@@ -28070,7 +28100,7 @@
           <t>HERZOG Andrea</t>
         </is>
       </c>
-      <c r="U477" t="inlineStr">
+      <c r="X477" t="inlineStr">
         <is>
           <t>55099</t>
         </is>
@@ -28128,7 +28158,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U478" t="inlineStr">
+      <c r="X478" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -28186,7 +28216,7 @@
           <t>OLAZABAL Klara</t>
         </is>
       </c>
-      <c r="U479" t="inlineStr">
+      <c r="X479" t="inlineStr">
         <is>
           <t>43985</t>
         </is>
@@ -28244,7 +28274,7 @@
           <t>GIBSON Eilidh</t>
         </is>
       </c>
-      <c r="U480" t="inlineStr">
+      <c r="X480" t="inlineStr">
         <is>
           <t>36708</t>
         </is>
@@ -28302,7 +28332,7 @@
           <t>FRANKLIN Mallory</t>
         </is>
       </c>
-      <c r="U481" t="inlineStr">
+      <c r="X481" t="inlineStr">
         <is>
           <t>35615</t>
         </is>
@@ -28360,7 +28390,7 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U482" t="inlineStr">
+      <c r="X482" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -28418,7 +28448,7 @@
           <t>VILARRUBLA Nuria</t>
         </is>
       </c>
-      <c r="U483" t="inlineStr">
+      <c r="X483" t="inlineStr">
         <is>
           <t>35746</t>
         </is>
@@ -28476,7 +28506,7 @@
           <t>BOWERS Christopher</t>
         </is>
       </c>
-      <c r="U484" t="inlineStr">
+      <c r="X484" t="inlineStr">
         <is>
           <t>52010</t>
         </is>
@@ -28534,7 +28564,7 @@
           <t>BERSINGER Thomas</t>
         </is>
       </c>
-      <c r="U485" t="inlineStr">
+      <c r="X485" t="inlineStr">
         <is>
           <t>35228</t>
         </is>
@@ -28592,7 +28622,7 @@
           <t>PASIUT Michal</t>
         </is>
       </c>
-      <c r="U486" t="inlineStr">
+      <c r="X486" t="inlineStr">
         <is>
           <t>35095</t>
         </is>
@@ -28650,7 +28680,7 @@
           <t>FORBES-CRYANS Bradley</t>
         </is>
       </c>
-      <c r="U487" t="inlineStr">
+      <c r="X487" t="inlineStr">
         <is>
           <t>36513</t>
         </is>
@@ -28708,7 +28738,7 @@
           <t>GRIGAR Jakub</t>
         </is>
       </c>
-      <c r="U488" t="inlineStr">
+      <c r="X488" t="inlineStr">
         <is>
           <t>37284</t>
         </is>
@@ -28766,7 +28796,7 @@
           <t>IVALDI Zeno</t>
         </is>
       </c>
-      <c r="U489" t="inlineStr">
+      <c r="X489" t="inlineStr">
         <is>
           <t>35480</t>
         </is>
@@ -28824,7 +28854,7 @@
           <t>SMOLEN Michal</t>
         </is>
       </c>
-      <c r="U490" t="inlineStr">
+      <c r="X490" t="inlineStr">
         <is>
           <t>36397</t>
         </is>
@@ -28882,7 +28912,7 @@
           <t>HOLMER Erik</t>
         </is>
       </c>
-      <c r="U491" t="inlineStr">
+      <c r="X491" t="inlineStr">
         <is>
           <t>35104</t>
         </is>
@@ -28940,7 +28970,7 @@
           <t>EIGEL Pavel</t>
         </is>
       </c>
-      <c r="U492" t="inlineStr">
+      <c r="X492" t="inlineStr">
         <is>
           <t>35458</t>
         </is>
@@ -28998,7 +29028,7 @@
           <t>CLARKE Joseph</t>
         </is>
       </c>
-      <c r="U493" t="inlineStr">
+      <c r="X493" t="inlineStr">
         <is>
           <t>35654</t>
         </is>
@@ -29056,7 +29086,7 @@
           <t>JAKSE Zan</t>
         </is>
       </c>
-      <c r="U494" t="inlineStr">
+      <c r="X494" t="inlineStr">
         <is>
           <t>44340</t>
         </is>
@@ -29114,7 +29144,7 @@
           <t>COMBOT Sebastien</t>
         </is>
       </c>
-      <c r="U495" t="inlineStr">
+      <c r="X495" t="inlineStr">
         <is>
           <t>35234</t>
         </is>
@@ -29172,7 +29202,7 @@
           <t>DOBY Mathieu</t>
         </is>
       </c>
-      <c r="U496" t="inlineStr">
+      <c r="X496" t="inlineStr">
         <is>
           <t>35292</t>
         </is>
@@ -29230,7 +29260,7 @@
           <t>VIANELLO Marco</t>
         </is>
       </c>
-      <c r="U497" t="inlineStr">
+      <c r="X497" t="inlineStr">
         <is>
           <t>54910</t>
         </is>
@@ -29288,7 +29318,7 @@
           <t>WEGER Matthias</t>
         </is>
       </c>
-      <c r="U498" t="inlineStr">
+      <c r="X498" t="inlineStr">
         <is>
           <t>68837</t>
         </is>
@@ -29346,7 +29376,7 @@
           <t>PRIGENT Yves</t>
         </is>
       </c>
-      <c r="U499" t="inlineStr">
+      <c r="X499" t="inlineStr">
         <is>
           <t>35671</t>
         </is>
@@ -29404,7 +29434,7 @@
           <t>SRABOTNIK Martin</t>
         </is>
       </c>
-      <c r="U500" t="inlineStr">
+      <c r="X500" t="inlineStr">
         <is>
           <t>39080</t>
         </is>
@@ -29462,7 +29492,7 @@
           <t>SCHWEIKERT Fabian</t>
         </is>
       </c>
-      <c r="U501" t="inlineStr">
+      <c r="X501" t="inlineStr">
         <is>
           <t>38412</t>
         </is>
@@ -29520,7 +29550,7 @@
           <t>LAUNAY Antoine</t>
         </is>
       </c>
-      <c r="U502" t="inlineStr">
+      <c r="X502" t="inlineStr">
         <is>
           <t>68776</t>
         </is>
@@ -29578,7 +29608,7 @@
           <t>PRINDIS Vit</t>
         </is>
       </c>
-      <c r="U503" t="inlineStr">
+      <c r="X503" t="inlineStr">
         <is>
           <t>35065</t>
         </is>
@@ -29636,7 +29666,7 @@
           <t>TUNKA Ondrej</t>
         </is>
       </c>
-      <c r="U504" t="inlineStr">
+      <c r="X504" t="inlineStr">
         <is>
           <t>35947</t>
         </is>
@@ -29694,7 +29724,7 @@
           <t>KAUZER Peter</t>
         </is>
       </c>
-      <c r="U505" t="inlineStr">
+      <c r="X505" t="inlineStr">
         <is>
           <t>35589</t>
         </is>
@@ -29752,7 +29782,7 @@
           <t>DE GENNARO Giovanni</t>
         </is>
       </c>
-      <c r="U506" t="inlineStr">
+      <c r="X506" t="inlineStr">
         <is>
           <t>35244</t>
         </is>
@@ -29810,7 +29840,7 @@
           <t>AIGNER Hannes</t>
         </is>
       </c>
-      <c r="U507" t="inlineStr">
+      <c r="X507" t="inlineStr">
         <is>
           <t>35115</t>
         </is>
@@ -29868,7 +29898,7 @@
           <t>LEITNER Mario</t>
         </is>
       </c>
-      <c r="U508" t="inlineStr">
+      <c r="X508" t="inlineStr">
         <is>
           <t>35546</t>
         </is>
@@ -29926,7 +29956,7 @@
           <t>DELFOUR Lucien</t>
         </is>
       </c>
-      <c r="U509" t="inlineStr">
+      <c r="X509" t="inlineStr">
         <is>
           <t>36537</t>
         </is>
@@ -29984,7 +30014,7 @@
           <t>LLORENTE David</t>
         </is>
       </c>
-      <c r="U510" t="inlineStr">
+      <c r="X510" t="inlineStr">
         <is>
           <t>51850</t>
         </is>
@@ -30042,7 +30072,7 @@
           <t>OSCHMAUTZ Felix</t>
         </is>
       </c>
-      <c r="U511" t="inlineStr">
+      <c r="X511" t="inlineStr">
         <is>
           <t>51856</t>
         </is>
@@ -30100,7 +30130,7 @@
           <t>SILVA Ivan</t>
         </is>
       </c>
-      <c r="U512" t="inlineStr">
+      <c r="X512" t="inlineStr">
         <is>
           <t>35482</t>
         </is>
@@ -30158,7 +30188,7 @@
           <t>BIAZIZZO Mathieu</t>
         </is>
       </c>
-      <c r="U513" t="inlineStr">
+      <c r="X513" t="inlineStr">
         <is>
           <t>35484</t>
         </is>
@@ -30216,7 +30246,7 @@
           <t>YAZAWA Kazuki</t>
         </is>
       </c>
-      <c r="U514" t="inlineStr">
+      <c r="X514" t="inlineStr">
         <is>
           <t>36482</t>
         </is>
@@ -30274,7 +30304,7 @@
           <t>SCHUBERT Sebastian</t>
         </is>
       </c>
-      <c r="U515" t="inlineStr">
+      <c r="X515" t="inlineStr">
         <is>
           <t>35114</t>
         </is>
@@ -30332,7 +30362,7 @@
           <t>CRESPO Joan</t>
         </is>
       </c>
-      <c r="U516" t="inlineStr">
+      <c r="X516" t="inlineStr">
         <is>
           <t>35749</t>
         </is>
@@ -30390,7 +30420,7 @@
           <t>HRADILEK Vavrinec</t>
         </is>
       </c>
-      <c r="U517" t="inlineStr">
+      <c r="X517" t="inlineStr">
         <is>
           <t>35031</t>
         </is>
@@ -30448,7 +30478,7 @@
           <t>POPIELA Dariusz</t>
         </is>
       </c>
-      <c r="U518" t="inlineStr">
+      <c r="X518" t="inlineStr">
         <is>
           <t>35096</t>
         </is>
@@ -30559,7 +30589,7 @@
           <t>HERNANZ Samuel</t>
         </is>
       </c>
-      <c r="U520" t="inlineStr">
+      <c r="X520" t="inlineStr">
         <is>
           <t>35786</t>
         </is>
@@ -30617,7 +30647,7 @@
           <t>POLACZYK Mateusz</t>
         </is>
       </c>
-      <c r="U521" t="inlineStr">
+      <c r="X521" t="inlineStr">
         <is>
           <t>35072</t>
         </is>
@@ -30675,7 +30705,7 @@
           <t>PRSKAVEC Jiri</t>
         </is>
       </c>
-      <c r="U522" t="inlineStr">
+      <c r="X522" t="inlineStr">
         <is>
           <t>35033</t>
         </is>
@@ -30733,7 +30763,7 @@
           <t>NEVEU Boris</t>
         </is>
       </c>
-      <c r="U523" t="inlineStr">
+      <c r="X523" t="inlineStr">
         <is>
           <t>35396</t>
         </is>
@@ -30806,12 +30836,12 @@
           <t>BATIK Jan</t>
         </is>
       </c>
-      <c r="U524" t="inlineStr">
+      <c r="X524" t="inlineStr">
         <is>
           <t>35368</t>
         </is>
       </c>
-      <c r="V524" t="inlineStr">
+      <c r="Y524" t="inlineStr">
         <is>
           <t>35367</t>
         </is>
@@ -30884,12 +30914,12 @@
           <t>VRZAN Jakub</t>
         </is>
       </c>
-      <c r="U525" t="inlineStr">
+      <c r="X525" t="inlineStr">
         <is>
           <t>35042</t>
         </is>
       </c>
-      <c r="V525" t="inlineStr">
+      <c r="Y525" t="inlineStr">
         <is>
           <t>35043</t>
         </is>
@@ -30962,12 +30992,12 @@
           <t>CAMPORESI Pietro</t>
         </is>
       </c>
-      <c r="U526" t="inlineStr">
+      <c r="X526" t="inlineStr">
         <is>
           <t>35498</t>
         </is>
       </c>
-      <c r="V526" t="inlineStr">
+      <c r="Y526" t="inlineStr">
         <is>
           <t>35497</t>
         </is>
@@ -31040,12 +31070,12 @@
           <t>BECKER Thomas</t>
         </is>
       </c>
-      <c r="U527" t="inlineStr">
+      <c r="X527" t="inlineStr">
         <is>
           <t>35139</t>
         </is>
       </c>
-      <c r="V527" t="inlineStr">
+      <c r="Y527" t="inlineStr">
         <is>
           <t>35143</t>
         </is>
@@ -31118,12 +31148,12 @@
           <t>HOCHSCHORNER Peter</t>
         </is>
       </c>
-      <c r="U528" t="inlineStr">
+      <c r="X528" t="inlineStr">
         <is>
           <t>35356</t>
         </is>
       </c>
-      <c r="V528" t="inlineStr">
+      <c r="Y528" t="inlineStr">
         <is>
           <t>35357</t>
         </is>
@@ -31196,12 +31226,12 @@
           <t>SKANTAR Peter</t>
         </is>
       </c>
-      <c r="U529" t="inlineStr">
+      <c r="X529" t="inlineStr">
         <is>
           <t>35360</t>
         </is>
       </c>
-      <c r="V529" t="inlineStr">
+      <c r="Y529" t="inlineStr">
         <is>
           <t>35361</t>
         </is>
@@ -31274,12 +31304,12 @@
           <t>BETTGE Nico</t>
         </is>
       </c>
-      <c r="U530" t="inlineStr">
+      <c r="X530" t="inlineStr">
         <is>
           <t>35145</t>
         </is>
       </c>
-      <c r="V530" t="inlineStr">
+      <c r="Y530" t="inlineStr">
         <is>
           <t>35133</t>
         </is>
@@ -31352,12 +31382,12 @@
           <t>JANE Jakub</t>
         </is>
       </c>
-      <c r="U531" t="inlineStr">
+      <c r="X531" t="inlineStr">
         <is>
           <t>35060</t>
         </is>
       </c>
-      <c r="V531" t="inlineStr">
+      <c r="Y531" t="inlineStr">
         <is>
           <t>35061</t>
         </is>
@@ -31430,12 +31460,12 @@
           <t>PECHE Matthieu</t>
         </is>
       </c>
-      <c r="U532" t="inlineStr">
+      <c r="X532" t="inlineStr">
         <is>
           <t>35350</t>
         </is>
       </c>
-      <c r="V532" t="inlineStr">
+      <c r="Y532" t="inlineStr">
         <is>
           <t>35400</t>
         </is>
@@ -31508,12 +31538,12 @@
           <t>SINDLER Marek</t>
         </is>
       </c>
-      <c r="U533" t="inlineStr">
+      <c r="X533" t="inlineStr">
         <is>
           <t>35062</t>
         </is>
       </c>
-      <c r="V533" t="inlineStr">
+      <c r="Y533" t="inlineStr">
         <is>
           <t>35063</t>
         </is>
@@ -31581,7 +31611,7 @@
           <t>VAN DER KNIJFF Annebel</t>
         </is>
       </c>
-      <c r="U534" t="inlineStr">
+      <c r="X534" t="inlineStr">
         <is>
           <t>39945</t>
         </is>
@@ -31649,7 +31679,7 @@
           <t>JACQUET Claire</t>
         </is>
       </c>
-      <c r="U535" t="inlineStr">
+      <c r="X535" t="inlineStr">
         <is>
           <t>35684</t>
         </is>
@@ -31717,7 +31747,7 @@
           <t>WOODS Kimberley</t>
         </is>
       </c>
-      <c r="U536" t="inlineStr">
+      <c r="X536" t="inlineStr">
         <is>
           <t>35650</t>
         </is>
@@ -31785,7 +31815,7 @@
           <t>JONES Luuka</t>
         </is>
       </c>
-      <c r="U537" t="inlineStr">
+      <c r="X537" t="inlineStr">
         <is>
           <t>36657</t>
         </is>
@@ -31853,7 +31883,7 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U538" t="inlineStr">
+      <c r="X538" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -31921,7 +31951,7 @@
           <t>WERATSCHNIG Nadine</t>
         </is>
       </c>
-      <c r="U539" t="inlineStr">
+      <c r="X539" t="inlineStr">
         <is>
           <t>41613</t>
         </is>
@@ -31989,7 +32019,7 @@
           <t>SATILA Ana</t>
         </is>
       </c>
-      <c r="U540" t="inlineStr">
+      <c r="X540" t="inlineStr">
         <is>
           <t>35327</t>
         </is>
@@ -32057,7 +32087,7 @@
           <t>VILARRUBLA Nuria</t>
         </is>
       </c>
-      <c r="U541" t="inlineStr">
+      <c r="X541" t="inlineStr">
         <is>
           <t>35746</t>
         </is>
@@ -32125,7 +32155,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U542" t="inlineStr">
+      <c r="X542" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -32193,7 +32223,7 @@
           <t>FRANKLIN Mallory</t>
         </is>
       </c>
-      <c r="U543" t="inlineStr">
+      <c r="X543" t="inlineStr">
         <is>
           <t>35615</t>
         </is>
@@ -32261,7 +32291,7 @@
           <t>SILVA Ivan</t>
         </is>
       </c>
-      <c r="U544" t="inlineStr">
+      <c r="X544" t="inlineStr">
         <is>
           <t>35482</t>
         </is>
@@ -32329,7 +32359,7 @@
           <t>SCHUBERT Sebastian</t>
         </is>
       </c>
-      <c r="U545" t="inlineStr">
+      <c r="X545" t="inlineStr">
         <is>
           <t>35114</t>
         </is>
@@ -32397,7 +32427,7 @@
           <t>JAKSE Zan</t>
         </is>
       </c>
-      <c r="U546" t="inlineStr">
+      <c r="X546" t="inlineStr">
         <is>
           <t>44340</t>
         </is>
@@ -32465,7 +32495,7 @@
           <t>CRESPO Joan</t>
         </is>
       </c>
-      <c r="U547" t="inlineStr">
+      <c r="X547" t="inlineStr">
         <is>
           <t>35749</t>
         </is>
@@ -32533,7 +32563,7 @@
           <t>PRINDIS Vit</t>
         </is>
       </c>
-      <c r="U548" t="inlineStr">
+      <c r="X548" t="inlineStr">
         <is>
           <t>35065</t>
         </is>
@@ -32601,7 +32631,7 @@
           <t>LLORENTE David</t>
         </is>
       </c>
-      <c r="U549" t="inlineStr">
+      <c r="X549" t="inlineStr">
         <is>
           <t>51850</t>
         </is>
@@ -32669,7 +32699,7 @@
           <t>COMBOT Sebastien</t>
         </is>
       </c>
-      <c r="U550" t="inlineStr">
+      <c r="X550" t="inlineStr">
         <is>
           <t>35234</t>
         </is>
@@ -32737,7 +32767,7 @@
           <t>NEVEU Boris</t>
         </is>
       </c>
-      <c r="U551" t="inlineStr">
+      <c r="X551" t="inlineStr">
         <is>
           <t>35396</t>
         </is>
@@ -32805,7 +32835,7 @@
           <t>KAUZER Peter</t>
         </is>
       </c>
-      <c r="U552" t="inlineStr">
+      <c r="X552" t="inlineStr">
         <is>
           <t>35589</t>
         </is>
@@ -32873,7 +32903,7 @@
           <t>PRSKAVEC Jiri</t>
         </is>
       </c>
-      <c r="U553" t="inlineStr">
+      <c r="X553" t="inlineStr">
         <is>
           <t>35033</t>
         </is>
@@ -33186,7 +33216,7 @@
           <t>ZWOLINSKA Klaudia</t>
         </is>
       </c>
-      <c r="U559" t="inlineStr">
+      <c r="X559" t="inlineStr">
         <is>
           <t>42027</t>
         </is>
@@ -33244,7 +33274,7 @@
           <t>LEENDERS Claudia</t>
         </is>
       </c>
-      <c r="U560" t="inlineStr">
+      <c r="X560" t="inlineStr">
         <is>
           <t>35331</t>
         </is>
@@ -33302,7 +33332,7 @@
           <t>GALUSKOVA Karolina</t>
         </is>
       </c>
-      <c r="U561" t="inlineStr">
+      <c r="X561" t="inlineStr">
         <is>
           <t>37266</t>
         </is>
@@ -33360,7 +33390,7 @@
           <t>BAUDU Lucie</t>
         </is>
       </c>
-      <c r="U562" t="inlineStr">
+      <c r="X562" t="inlineStr">
         <is>
           <t>35669</t>
         </is>
@@ -33418,7 +33448,7 @@
           <t>HORN Stefanie</t>
         </is>
       </c>
-      <c r="U563" t="inlineStr">
+      <c r="X563" t="inlineStr">
         <is>
           <t>38417</t>
         </is>
@@ -33476,7 +33506,7 @@
           <t>KHARITONOVA Marta</t>
         </is>
       </c>
-      <c r="U564" t="inlineStr">
+      <c r="X564" t="inlineStr">
         <is>
           <t>35257</t>
         </is>
@@ -33534,7 +33564,7 @@
           <t>LAWRENCE Rosalyn</t>
         </is>
       </c>
-      <c r="U565" t="inlineStr">
+      <c r="X565" t="inlineStr">
         <is>
           <t>36531</t>
         </is>
@@ -33592,7 +33622,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U566" t="inlineStr">
+      <c r="X566" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -33650,7 +33680,7 @@
           <t>LI Tong</t>
         </is>
       </c>
-      <c r="U567" t="inlineStr">
+      <c r="X567" t="inlineStr">
         <is>
           <t>52023</t>
         </is>
@@ -33708,7 +33738,7 @@
           <t>LEITNER Lisa</t>
         </is>
       </c>
-      <c r="U568" t="inlineStr">
+      <c r="X568" t="inlineStr">
         <is>
           <t>35305</t>
         </is>
@@ -33766,7 +33796,7 @@
           <t>ECKHARDT Kate</t>
         </is>
       </c>
-      <c r="U569" t="inlineStr">
+      <c r="X569" t="inlineStr">
         <is>
           <t>44815</t>
         </is>
@@ -33824,7 +33854,7 @@
           <t>MARTINEZ Marta</t>
         </is>
       </c>
-      <c r="U570" t="inlineStr">
+      <c r="X570" t="inlineStr">
         <is>
           <t>35760</t>
         </is>
@@ -33882,7 +33912,7 @@
           <t>GIAI PRON Maria Clara</t>
         </is>
       </c>
-      <c r="U571" t="inlineStr">
+      <c r="X571" t="inlineStr">
         <is>
           <t>35218</t>
         </is>
@@ -33940,7 +33970,7 @@
           <t>SABATTINI Chiara</t>
         </is>
       </c>
-      <c r="U572" t="inlineStr">
+      <c r="X572" t="inlineStr">
         <is>
           <t>35219</t>
         </is>
@@ -33998,7 +34028,7 @@
           <t>LAFONT Marie-Zelia</t>
         </is>
       </c>
-      <c r="U573" t="inlineStr">
+      <c r="X573" t="inlineStr">
         <is>
           <t>35374</t>
         </is>
@@ -34056,7 +34086,7 @@
           <t>PACIERPNIK Natalia</t>
         </is>
       </c>
-      <c r="U574" t="inlineStr">
+      <c r="X574" t="inlineStr">
         <is>
           <t>35077</t>
         </is>
@@ -34114,7 +34144,7 @@
           <t>TERCELJ Eva</t>
         </is>
       </c>
-      <c r="U575" t="inlineStr">
+      <c r="X575" t="inlineStr">
         <is>
           <t>36263</t>
         </is>
@@ -34172,7 +34202,7 @@
           <t>KUDEJOVA Katerina</t>
         </is>
       </c>
-      <c r="U576" t="inlineStr">
+      <c r="X576" t="inlineStr">
         <is>
           <t>35034</t>
         </is>
@@ -34230,7 +34260,7 @@
           <t>FRANKLIN Mallory</t>
         </is>
       </c>
-      <c r="U577" t="inlineStr">
+      <c r="X577" t="inlineStr">
         <is>
           <t>35615</t>
         </is>
@@ -34288,7 +34318,7 @@
           <t>KRAGELJ Ursa</t>
         </is>
       </c>
-      <c r="U578" t="inlineStr">
+      <c r="X578" t="inlineStr">
         <is>
           <t>36264</t>
         </is>
@@ -34346,7 +34376,7 @@
           <t>WOODS Kimberley</t>
         </is>
       </c>
-      <c r="U579" t="inlineStr">
+      <c r="X579" t="inlineStr">
         <is>
           <t>35650</t>
         </is>
@@ -34404,7 +34434,7 @@
           <t>BOUZIDI Carole</t>
         </is>
       </c>
-      <c r="U580" t="inlineStr">
+      <c r="X580" t="inlineStr">
         <is>
           <t>35231</t>
         </is>
@@ -34462,7 +34492,7 @@
           <t>SATILA Ana</t>
         </is>
       </c>
-      <c r="U581" t="inlineStr">
+      <c r="X581" t="inlineStr">
         <is>
           <t>35327</t>
         </is>
@@ -34520,7 +34550,7 @@
           <t>SCHORNBERG Jasmin</t>
         </is>
       </c>
-      <c r="U582" t="inlineStr">
+      <c r="X582" t="inlineStr">
         <is>
           <t>35206</t>
         </is>
@@ -34578,7 +34608,7 @@
           <t>CHOURRAUT Maialen</t>
         </is>
       </c>
-      <c r="U583" t="inlineStr">
+      <c r="X583" t="inlineStr">
         <is>
           <t>35787</t>
         </is>
@@ -34636,7 +34666,7 @@
           <t>DUKATOVA Jana</t>
         </is>
       </c>
-      <c r="U584" t="inlineStr">
+      <c r="X584" t="inlineStr">
         <is>
           <t>35354</t>
         </is>
@@ -34694,7 +34724,7 @@
           <t>KUHNLE Corinna</t>
         </is>
       </c>
-      <c r="U585" t="inlineStr">
+      <c r="X585" t="inlineStr">
         <is>
           <t>35282</t>
         </is>
@@ -34752,7 +34782,7 @@
           <t>PENNIE Fiona</t>
         </is>
       </c>
-      <c r="U586" t="inlineStr">
+      <c r="X586" t="inlineStr">
         <is>
           <t>35638</t>
         </is>
@@ -34810,7 +34840,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U587" t="inlineStr">
+      <c r="X587" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -34868,7 +34898,7 @@
           <t>FUNK Ricarda</t>
         </is>
       </c>
-      <c r="U588" t="inlineStr">
+      <c r="X588" t="inlineStr">
         <is>
           <t>35122</t>
         </is>
@@ -34926,7 +34956,7 @@
           <t>SZCZEPANSKI Piotr</t>
         </is>
       </c>
-      <c r="U589" t="inlineStr">
+      <c r="X589" t="inlineStr">
         <is>
           <t>35080</t>
         </is>
@@ -34984,7 +35014,7 @@
           <t>HANEDA Takuya</t>
         </is>
       </c>
-      <c r="U590" t="inlineStr">
+      <c r="X590" t="inlineStr">
         <is>
           <t>36481</t>
         </is>
@@ -35042,7 +35072,7 @@
           <t>CHALOUPKA Vaclav</t>
         </is>
       </c>
-      <c r="U591" t="inlineStr">
+      <c r="X591" t="inlineStr">
         <is>
           <t>51648</t>
         </is>
@@ -35100,7 +35130,7 @@
           <t>LE RUYET Edern</t>
         </is>
       </c>
-      <c r="U592" t="inlineStr">
+      <c r="X592" t="inlineStr">
         <is>
           <t>35379</t>
         </is>
@@ -35158,7 +35188,7 @@
           <t>GEBAS Vitezslav</t>
         </is>
       </c>
-      <c r="U593" t="inlineStr">
+      <c r="X593" t="inlineStr">
         <is>
           <t>35038</t>
         </is>
@@ -35216,7 +35246,7 @@
           <t>MARC Jonathan</t>
         </is>
       </c>
-      <c r="U594" t="inlineStr">
+      <c r="X594" t="inlineStr">
         <is>
           <t>35388</t>
         </is>
@@ -35274,7 +35304,7 @@
           <t>SZTUBA Kacper</t>
         </is>
       </c>
-      <c r="U595" t="inlineStr">
+      <c r="X595" t="inlineStr">
         <is>
           <t>53636</t>
         </is>
@@ -35332,7 +35362,7 @@
           <t>HEDWIG Grzegorz</t>
         </is>
       </c>
-      <c r="U596" t="inlineStr">
+      <c r="X596" t="inlineStr">
         <is>
           <t>35465</t>
         </is>
@@ -35390,7 +35420,7 @@
           <t>GARGAUD CHANUT Denis</t>
         </is>
       </c>
-      <c r="U597" t="inlineStr">
+      <c r="X597" t="inlineStr">
         <is>
           <t>35177</t>
         </is>
@@ -35448,7 +35478,7 @@
           <t>BOZIC Luka</t>
         </is>
       </c>
-      <c r="U598" t="inlineStr">
+      <c r="X598" t="inlineStr">
         <is>
           <t>36269</t>
         </is>
@@ -35506,7 +35536,7 @@
           <t>BADURA Jergus</t>
         </is>
       </c>
-      <c r="U599" t="inlineStr">
+      <c r="X599" t="inlineStr">
         <is>
           <t>68767</t>
         </is>
@@ -35564,7 +35594,7 @@
           <t>EICHFELD Casey</t>
         </is>
       </c>
-      <c r="U600" t="inlineStr">
+      <c r="X600" t="inlineStr">
         <is>
           <t>35067</t>
         </is>
@@ -35622,7 +35652,7 @@
           <t>IVALDI Raffaello</t>
         </is>
       </c>
-      <c r="U601" t="inlineStr">
+      <c r="X601" t="inlineStr">
         <is>
           <t>35227</t>
         </is>
@@ -35680,7 +35710,7 @@
           <t>CIPRESSI Stefano</t>
         </is>
       </c>
-      <c r="U602" t="inlineStr">
+      <c r="X602" t="inlineStr">
         <is>
           <t>35495</t>
         </is>
@@ -35738,7 +35768,7 @@
           <t>SETKIN Kirill</t>
         </is>
       </c>
-      <c r="U603" t="inlineStr">
+      <c r="X603" t="inlineStr">
         <is>
           <t>35457</t>
         </is>
@@ -35796,7 +35826,7 @@
           <t>ELOSEGI Ander</t>
         </is>
       </c>
-      <c r="U604" t="inlineStr">
+      <c r="X604" t="inlineStr">
         <is>
           <t>35785</t>
         </is>
@@ -35854,7 +35884,7 @@
           <t>BERCIC Anze</t>
         </is>
       </c>
-      <c r="U605" t="inlineStr">
+      <c r="X605" t="inlineStr">
         <is>
           <t>36253</t>
         </is>
@@ -35912,7 +35942,7 @@
           <t>BENUS Matej</t>
         </is>
       </c>
-      <c r="U606" t="inlineStr">
+      <c r="X606" t="inlineStr">
         <is>
           <t>35353</t>
         </is>
@@ -35970,7 +36000,7 @@
           <t>COLAZINGARI Roberto</t>
         </is>
       </c>
-      <c r="U607" t="inlineStr">
+      <c r="X607" t="inlineStr">
         <is>
           <t>35223</t>
         </is>
@@ -36028,7 +36058,7 @@
           <t>BURGESS Adam</t>
         </is>
       </c>
-      <c r="U608" t="inlineStr">
+      <c r="X608" t="inlineStr">
         <is>
           <t>35647</t>
         </is>
@@ -36086,7 +36116,7 @@
           <t>FLORENCE David</t>
         </is>
       </c>
-      <c r="U609" t="inlineStr">
+      <c r="X609" t="inlineStr">
         <is>
           <t>35634</t>
         </is>
@@ -36144,7 +36174,7 @@
           <t>THOMAS Martin</t>
         </is>
       </c>
-      <c r="U610" t="inlineStr">
+      <c r="X610" t="inlineStr">
         <is>
           <t>35412</t>
         </is>
@@ -36202,7 +36232,7 @@
           <t>SMEDLEY Cameron</t>
         </is>
       </c>
-      <c r="U611" t="inlineStr">
+      <c r="X611" t="inlineStr">
         <is>
           <t>35543</t>
         </is>
@@ -36260,7 +36290,7 @@
           <t>ANTON Franz</t>
         </is>
       </c>
-      <c r="U612" t="inlineStr">
+      <c r="X612" t="inlineStr">
         <is>
           <t>35137</t>
         </is>
@@ -36318,7 +36348,7 @@
           <t>WESTLEY Ryan</t>
         </is>
       </c>
-      <c r="U613" t="inlineStr">
+      <c r="X613" t="inlineStr">
         <is>
           <t>35651</t>
         </is>
@@ -36376,7 +36406,7 @@
           <t>ROHAN Lukas</t>
         </is>
       </c>
-      <c r="U614" t="inlineStr">
+      <c r="X614" t="inlineStr">
         <is>
           <t>36114</t>
         </is>
@@ -36434,7 +36464,7 @@
           <t>MARTIKAN Michal</t>
         </is>
       </c>
-      <c r="U615" t="inlineStr">
+      <c r="X615" t="inlineStr">
         <is>
           <t>35365</t>
         </is>
@@ -36492,7 +36522,7 @@
           <t>SAVSEK Benjamin</t>
         </is>
       </c>
-      <c r="U616" t="inlineStr">
+      <c r="X616" t="inlineStr">
         <is>
           <t>36218</t>
         </is>
@@ -36550,7 +36580,7 @@
           <t>TASIADIS Sideris</t>
         </is>
       </c>
-      <c r="U617" t="inlineStr">
+      <c r="X617" t="inlineStr">
         <is>
           <t>35135</t>
         </is>
@@ -36608,7 +36638,7 @@
           <t>SLAFKOVSKY Alexander</t>
         </is>
       </c>
-      <c r="U618" t="inlineStr">
+      <c r="X618" t="inlineStr">
         <is>
           <t>35129</t>
         </is>
@@ -36676,7 +36706,7 @@
           <t>DUKATOVA Jana</t>
         </is>
       </c>
-      <c r="U619" t="inlineStr">
+      <c r="X619" t="inlineStr">
         <is>
           <t>35354</t>
         </is>
@@ -36744,7 +36774,7 @@
           <t>KHARITONOVA Marta</t>
         </is>
       </c>
-      <c r="U620" t="inlineStr">
+      <c r="X620" t="inlineStr">
         <is>
           <t>35257</t>
         </is>
@@ -36812,7 +36842,7 @@
           <t>PACIERPNIK Natalia</t>
         </is>
       </c>
-      <c r="U621" t="inlineStr">
+      <c r="X621" t="inlineStr">
         <is>
           <t>35077</t>
         </is>
@@ -36880,7 +36910,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U622" t="inlineStr">
+      <c r="X622" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -36948,7 +36978,7 @@
           <t>KUDEJOVA Katerina</t>
         </is>
       </c>
-      <c r="U623" t="inlineStr">
+      <c r="X623" t="inlineStr">
         <is>
           <t>35034</t>
         </is>
@@ -37016,7 +37046,7 @@
           <t>MARTINEZ Marta</t>
         </is>
       </c>
-      <c r="U624" t="inlineStr">
+      <c r="X624" t="inlineStr">
         <is>
           <t>35760</t>
         </is>
@@ -37084,7 +37114,7 @@
           <t>KRAGELJ Ursa</t>
         </is>
       </c>
-      <c r="U625" t="inlineStr">
+      <c r="X625" t="inlineStr">
         <is>
           <t>36264</t>
         </is>
@@ -37152,7 +37182,7 @@
           <t>CHOURRAUT Maialen</t>
         </is>
       </c>
-      <c r="U626" t="inlineStr">
+      <c r="X626" t="inlineStr">
         <is>
           <t>35787</t>
         </is>
@@ -37220,7 +37250,7 @@
           <t>FUNK Ricarda</t>
         </is>
       </c>
-      <c r="U627" t="inlineStr">
+      <c r="X627" t="inlineStr">
         <is>
           <t>35122</t>
         </is>
@@ -37288,7 +37318,7 @@
           <t>SATILA Ana</t>
         </is>
       </c>
-      <c r="U628" t="inlineStr">
+      <c r="X628" t="inlineStr">
         <is>
           <t>35327</t>
         </is>
@@ -37356,7 +37386,7 @@
           <t>BERCIC Anze</t>
         </is>
       </c>
-      <c r="U629" t="inlineStr">
+      <c r="X629" t="inlineStr">
         <is>
           <t>36253</t>
         </is>
@@ -37424,7 +37454,7 @@
           <t>ROHAN Lukas</t>
         </is>
       </c>
-      <c r="U630" t="inlineStr">
+      <c r="X630" t="inlineStr">
         <is>
           <t>36114</t>
         </is>
@@ -37492,7 +37522,7 @@
           <t>WESTLEY Ryan</t>
         </is>
       </c>
-      <c r="U631" t="inlineStr">
+      <c r="X631" t="inlineStr">
         <is>
           <t>35651</t>
         </is>
@@ -37560,7 +37590,7 @@
           <t>CHALOUPKA Vaclav</t>
         </is>
       </c>
-      <c r="U632" t="inlineStr">
+      <c r="X632" t="inlineStr">
         <is>
           <t>51648</t>
         </is>
@@ -37628,7 +37658,7 @@
           <t>HEDWIG Grzegorz</t>
         </is>
       </c>
-      <c r="U633" t="inlineStr">
+      <c r="X633" t="inlineStr">
         <is>
           <t>35465</t>
         </is>
@@ -37696,7 +37726,7 @@
           <t>HANEDA Takuya</t>
         </is>
       </c>
-      <c r="U634" t="inlineStr">
+      <c r="X634" t="inlineStr">
         <is>
           <t>36481</t>
         </is>
@@ -37764,7 +37794,7 @@
           <t>SLAFKOVSKY Alexander</t>
         </is>
       </c>
-      <c r="U635" t="inlineStr">
+      <c r="X635" t="inlineStr">
         <is>
           <t>35129</t>
         </is>
@@ -37832,7 +37862,7 @@
           <t>THOMAS Martin</t>
         </is>
       </c>
-      <c r="U636" t="inlineStr">
+      <c r="X636" t="inlineStr">
         <is>
           <t>35412</t>
         </is>
@@ -37900,7 +37930,7 @@
           <t>ELOSEGI Ander</t>
         </is>
       </c>
-      <c r="U637" t="inlineStr">
+      <c r="X637" t="inlineStr">
         <is>
           <t>35785</t>
         </is>
@@ -37968,7 +37998,7 @@
           <t>SAVSEK Benjamin</t>
         </is>
       </c>
-      <c r="U638" t="inlineStr">
+      <c r="X638" t="inlineStr">
         <is>
           <t>36218</t>
         </is>
@@ -38036,7 +38066,7 @@
           <t>TASIADIS Sideris</t>
         </is>
       </c>
-      <c r="U639" t="inlineStr">
+      <c r="X639" t="inlineStr">
         <is>
           <t>35135</t>
         </is>
